--- a/model/Outputs/11. Interest rate/10/Output Files/0.1/Output_18_47.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.1/Output_18_47.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5717662.902390703</v>
+        <v>5717790.953753835</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13052476.69608441</v>
+        <v>13052476.69608429</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13052476.69608441</v>
+        <v>13052476.69608429</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1002742.516426042</v>
+        <v>1002742.516425944</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1002742.516426042</v>
+        <v>1002742.516425944</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39020031.84654357</v>
+        <v>39020031.84654365</v>
       </c>
     </row>
   </sheetData>
@@ -660,7 +660,7 @@
         <v>42.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>3.339155739849787</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -708,7 +708,7 @@
         <v>81.71042910885558</v>
       </c>
       <c r="T2" t="n">
-        <v>154.2098088515635</v>
+        <v>157.5489645914134</v>
       </c>
       <c r="U2" t="n">
         <v>242.1997488099172</v>
@@ -745,7 +745,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>297.7419329688734</v>
       </c>
       <c r="G3" t="n">
         <v>325.5954226674802</v>
@@ -754,7 +754,7 @@
         <v>330.7762569977419</v>
       </c>
       <c r="I3" t="n">
-        <v>212.1645934385184</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -799,7 +799,7 @@
         <v>25.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>98.44007897576445</v>
+        <v>12.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
         <v>81.71042910885556</v>
       </c>
       <c r="T5" t="n">
-        <v>178.4965164019307</v>
+        <v>154.2098088515635</v>
       </c>
       <c r="U5" t="n">
         <v>242.1997488099172</v>
@@ -954,7 +954,7 @@
         <v>222.8510241668239</v>
       </c>
       <c r="W5" t="n">
-        <v>207.0867684305803</v>
+        <v>231.3734759809475</v>
       </c>
       <c r="X5" t="n">
         <v>185.2818334606677</v>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>278.304254857587</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>212.1645934385184</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>154.6833405621777</v>
       </c>
       <c r="R6" t="n">
-        <v>346</v>
+        <v>131.3261369150208</v>
       </c>
       <c r="S6" t="n">
-        <v>346</v>
+        <v>56.88716034196979</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1030,13 +1030,13 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>245.6729836441044</v>
+        <v>7.510667191520156</v>
       </c>
       <c r="W6" t="n">
         <v>25.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>12.86273944538755</v>
+        <v>346</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1088,13 +1088,13 @@
         <v>145.6963703536521</v>
       </c>
       <c r="O7" t="n">
-        <v>213.6406412628698</v>
+        <v>216.3682526036051</v>
       </c>
       <c r="P7" t="n">
         <v>265.835307164343</v>
       </c>
       <c r="Q7" t="n">
-        <v>308.722266425598</v>
+        <v>305.9946550848628</v>
       </c>
       <c r="R7" t="n">
         <v>314.1696361778723</v>
@@ -1134,7 +1134,7 @@
         <v>42.47457824299391</v>
       </c>
       <c r="D8" t="n">
-        <v>3.339155739849787</v>
+        <v>2.337248189482466</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1179,10 +1179,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>81.71042910885558</v>
+        <v>81.71042910885556</v>
       </c>
       <c r="T8" t="n">
-        <v>178.4965164019308</v>
+        <v>178.4965164019307</v>
       </c>
       <c r="U8" t="n">
         <v>242.1997488099172</v>
@@ -1191,7 +1191,7 @@
         <v>222.8510241668239</v>
       </c>
       <c r="W8" t="n">
-        <v>230.3715684305803</v>
+        <v>231.3734759809475</v>
       </c>
       <c r="X8" t="n">
         <v>185.2818334606677</v>
@@ -1252,28 +1252,28 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>154.6833405621777</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>352</v>
+        <v>352.0000000000106</v>
       </c>
       <c r="S9" t="n">
-        <v>352</v>
+        <v>56.88716034196979</v>
       </c>
       <c r="T9" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>352.0000000000069</v>
       </c>
       <c r="V9" t="n">
         <v>7.510667191520156</v>
       </c>
       <c r="W9" t="n">
-        <v>25.37314290982852</v>
+        <v>352.0000000000069</v>
       </c>
       <c r="X9" t="n">
-        <v>100.2332136513237</v>
+        <v>223.4025367813356</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>94.69257861566462</v>
+        <v>94.69257861566464</v>
       </c>
       <c r="N10" t="n">
         <v>145.6963703536521</v>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81.99931295557451</v>
+        <v>20.17085006969396</v>
       </c>
       <c r="C11" t="n">
         <v>49.47457824299391</v>
@@ -1380,10 +1380,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G11" t="n">
-        <v>3.488025553347868</v>
+        <v>3.488025553347882</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>5.251211467346479</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,10 +1416,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>88.71042910885556</v>
+        <v>88.71042910885558</v>
       </c>
       <c r="T11" t="n">
-        <v>128.9192649833349</v>
+        <v>185.4965164019308</v>
       </c>
       <c r="U11" t="n">
         <v>249.1997488099172</v>
@@ -1447,7 +1447,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>359.0000000000164</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -1456,13 +1456,13 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>325.5954226674802</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>330.7762569977419</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1489,19 +1489,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>154.6833405621777</v>
       </c>
       <c r="R12" t="n">
         <v>138.3261369150208</v>
       </c>
       <c r="S12" t="n">
-        <v>137.7419893628595</v>
+        <v>280.9293102491354</v>
       </c>
       <c r="T12" t="n">
-        <v>4.776887859023249</v>
+        <v>4.776887859023248</v>
       </c>
       <c r="U12" t="n">
-        <v>0.200878628111276</v>
+        <v>0.2008786281112975</v>
       </c>
       <c r="V12" t="n">
         <v>14.51066719152016</v>
@@ -1510,7 +1510,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X12" t="n">
-        <v>19.86273944538755</v>
+        <v>359.0000000000164</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>5.585037993844747</v>
+        <v>5.585037993844765</v>
       </c>
       <c r="M13" t="n">
         <v>101.6925786156646</v>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.42376838451291</v>
+        <v>74.00871791955517</v>
       </c>
       <c r="C14" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>10.33915573984979</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G14" t="n">
         <v>3.488025553347868</v>
@@ -1681,19 +1681,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>170.1242283498908</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1702,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>212.1645934385184</v>
+        <v>9.190653802055946</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1750,7 +1750,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>359.0000000000101</v>
       </c>
     </row>
     <row r="16">
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.251211467346504</v>
+        <v>1.251211467346479</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1890,10 +1890,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>78.87177793143506</v>
+        <v>78.87177793148999</v>
       </c>
       <c r="T17" t="n">
-        <v>181.4965164019307</v>
+        <v>181.4965164019308</v>
       </c>
       <c r="U17" t="n">
         <v>245.1997488099172</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1963,31 +1963,31 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>154.6833405621777</v>
       </c>
       <c r="R18" t="n">
         <v>134.3261369150208</v>
       </c>
       <c r="S18" t="n">
-        <v>59.88716034196979</v>
+        <v>59.88716034196977</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7768878590232496</v>
+        <v>0.7768878590232475</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>260.2640991912509</v>
       </c>
       <c r="V18" t="n">
-        <v>10.51066719152016</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="W18" t="n">
-        <v>61.29951200731619</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="X18" t="n">
-        <v>359</v>
+        <v>15.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2027,10 +2027,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.585037993844747</v>
+        <v>1.585037993844765</v>
       </c>
       <c r="M19" t="n">
-        <v>97.69257861566464</v>
+        <v>97.69257861566462</v>
       </c>
       <c r="N19" t="n">
         <v>148.6963703536521</v>
@@ -2082,7 +2082,7 @@
         <v>45.47457824299391</v>
       </c>
       <c r="D20" t="n">
-        <v>6.339155739849787</v>
+        <v>0.5005045624839758</v>
       </c>
       <c r="E20" t="n">
         <v>0.3632896068686478</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>78.87177793143326</v>
+        <v>84.71042910885558</v>
       </c>
       <c r="T20" t="n">
         <v>181.4965164019308</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>359</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>43.43703628897744</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>359</v>
+        <v>134.3261369150208</v>
       </c>
       <c r="S21" t="n">
         <v>59.88716034196977</v>
@@ -2215,16 +2215,16 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>359</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="W21" t="n">
         <v>28.37314290982852</v>
       </c>
       <c r="X21" t="n">
-        <v>15.86273944538755</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="Y21" t="n">
-        <v>161.9004337586411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2322,7 +2322,7 @@
         <v>6.339155739849787</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.3632896068686478</v>
       </c>
       <c r="F23" t="n">
         <v>0.8896287080118555</v>
@@ -2331,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5017861550836462</v>
+        <v>0.5017861551637537</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>181.4965164019307</v>
       </c>
       <c r="U23" t="n">
-        <v>240.473812551618</v>
+        <v>240.1105229447311</v>
       </c>
       <c r="V23" t="n">
         <v>225.8510241668239</v>
@@ -2401,10 +2401,10 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2440,22 +2440,22 @@
         <v>154.6833405621777</v>
       </c>
       <c r="R24" t="n">
-        <v>359</v>
+        <v>134.3261369150208</v>
       </c>
       <c r="S24" t="n">
-        <v>92.28524678712361</v>
+        <v>59.88716034196979</v>
       </c>
       <c r="T24" t="n">
         <v>0.7768878590232496</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>359.0000000000102</v>
       </c>
       <c r="V24" t="n">
-        <v>10.51066719152016</v>
+        <v>359.0000000000102</v>
       </c>
       <c r="W24" t="n">
-        <v>28.37314290982852</v>
+        <v>260.2640991912505</v>
       </c>
       <c r="X24" t="n">
         <v>15.86273944538755</v>
@@ -2553,22 +2553,22 @@
         <v>125.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>93.47457824299391</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>54.33915573984979</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>48.36328960686865</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>48.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>47.48802555334788</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>49.25121146734648</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,19 +2601,19 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>132.7104291088556</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>293.1997488099172</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>265.1081961100864</v>
+        <v>273.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>282.3734759809475</v>
+        <v>92.31407830691492</v>
       </c>
       <c r="X26" t="n">
         <v>236.2818334606677</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28.55655664632661</v>
+        <v>85.21512079324906</v>
       </c>
       <c r="C27" t="n">
         <v>5.099912445519294</v>
@@ -2674,19 +2674,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>154.6833405621777</v>
       </c>
       <c r="R27" t="n">
-        <v>350</v>
+        <v>350.0000000000235</v>
       </c>
       <c r="S27" t="n">
         <v>107.8871603419698</v>
       </c>
       <c r="T27" t="n">
-        <v>260.1187925681637</v>
+        <v>48.77688785902325</v>
       </c>
       <c r="U27" t="n">
-        <v>350</v>
+        <v>350.000000000017</v>
       </c>
       <c r="V27" t="n">
         <v>58.51066719152016</v>
@@ -2744,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>69.80851790624563</v>
+        <v>196.6963703536521</v>
       </c>
       <c r="O28" t="n">
         <v>267.3682526036051</v>
@@ -2753,13 +2753,13 @@
         <v>316.835307164343</v>
       </c>
       <c r="Q28" t="n">
-        <v>350</v>
+        <v>227.3800698784444</v>
       </c>
       <c r="R28" t="n">
-        <v>350</v>
+        <v>350.000000000017</v>
       </c>
       <c r="S28" t="n">
-        <v>4.267922325806239</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2796,10 +2796,10 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>42.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>42.88962870801186</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2838,13 +2838,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>126.7104291088556</v>
       </c>
       <c r="T29" t="n">
-        <v>104.0052734314906</v>
+        <v>179.2416748177336</v>
       </c>
       <c r="U29" t="n">
-        <v>287.1997488099172</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>267.8510241668239</v>
@@ -2866,13 +2866,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22.55655664632661</v>
+        <v>51.68573735945595</v>
       </c>
       <c r="C30" t="n">
-        <v>14.90498672754159</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2887,7 +2887,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>212.1645934385184</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2911,16 +2911,16 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>154.6833405621777</v>
       </c>
       <c r="R30" t="n">
-        <v>350</v>
+        <v>176.3261369150208</v>
       </c>
       <c r="S30" t="n">
-        <v>350</v>
+        <v>101.8871603419698</v>
       </c>
       <c r="T30" t="n">
-        <v>350</v>
+        <v>42.77688785902325</v>
       </c>
       <c r="U30" t="n">
         <v>38.20087862811128</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>43.58503799384475</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>310.835307164343</v>
       </c>
       <c r="Q31" t="n">
-        <v>201.7950318845549</v>
+        <v>245.3800698784462</v>
       </c>
       <c r="R31" t="n">
-        <v>350</v>
+        <v>350.0000000000152</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3030,7 +3030,7 @@
         <v>39.47457824299391</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>0.3391557398497866</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -3087,13 +3087,13 @@
         <v>219.8510241668239</v>
       </c>
       <c r="W32" t="n">
-        <v>228.3734759809475</v>
+        <v>226.325168430642</v>
       </c>
       <c r="X32" t="n">
         <v>182.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>99.60828087228884</v>
+        <v>101.3174326828064</v>
       </c>
     </row>
     <row r="33">
@@ -3103,16 +3103,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>274.6799154122626</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>344.0000000000128</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -3148,16 +3148,16 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>154.6833405621777</v>
       </c>
       <c r="R33" t="n">
-        <v>234.7346330211224</v>
+        <v>128.3261369150208</v>
       </c>
       <c r="S33" t="n">
         <v>53.88716034196979</v>
       </c>
       <c r="T33" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3166,7 +3166,7 @@
         <v>4.510667191520156</v>
       </c>
       <c r="W33" t="n">
-        <v>344</v>
+        <v>22.37314290982852</v>
       </c>
       <c r="X33" t="n">
         <v>9.862739445387547</v>
@@ -3352,16 +3352,16 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>330.7762569977419</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>212.1645934385184</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3385,10 +3385,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>119.1056355514891</v>
       </c>
       <c r="R36" t="n">
-        <v>337</v>
+        <v>125.3261369150208</v>
       </c>
       <c r="S36" t="n">
         <v>50.88716034196979</v>
@@ -3397,19 +3397,19 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>12.25503967503381</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>1.510667191520156</v>
       </c>
       <c r="W36" t="n">
-        <v>19.37314290982852</v>
+        <v>337</v>
       </c>
       <c r="X36" t="n">
-        <v>6.862739445387547</v>
+        <v>337</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
     </row>
     <row r="37">
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>87.03776727492934</v>
+        <v>88.69257861566464</v>
       </c>
       <c r="N37" t="n">
         <v>139.6963703536521</v>
@@ -3461,7 +3461,7 @@
         <v>210.3682526036051</v>
       </c>
       <c r="P37" t="n">
-        <v>259.835307164343</v>
+        <v>258.1804958236077</v>
       </c>
       <c r="Q37" t="n">
         <v>302.722266425598</v>
@@ -3549,10 +3549,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>73.83567729833796</v>
+        <v>73.83567729833818</v>
       </c>
       <c r="T38" t="n">
-        <v>172.4965164019308</v>
+        <v>172.4965164019307</v>
       </c>
       <c r="U38" t="n">
         <v>236.1997488099172</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>212.1645934385184</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3622,28 +3622,28 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>154.6833405621777</v>
       </c>
       <c r="R39" t="n">
         <v>125.3261369150208</v>
       </c>
       <c r="S39" t="n">
-        <v>268.5923200997246</v>
+        <v>50.88716034196979</v>
       </c>
       <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
         <v>337</v>
       </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.510667191520156</v>
-      </c>
       <c r="W39" t="n">
-        <v>19.37314290982852</v>
+        <v>337</v>
       </c>
       <c r="X39" t="n">
-        <v>6.862739445387547</v>
+        <v>302.9329621808317</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>87.03776727492934</v>
+        <v>88.69257861566464</v>
       </c>
       <c r="N40" t="n">
         <v>139.6963703536521</v>
@@ -3704,7 +3704,7 @@
         <v>302.722266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>308.1696361778723</v>
+        <v>306.5148248371369</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3738,22 +3738,22 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>136.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>97.33915573984979</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>29.98436836812661</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>91.88962870801186</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>92.25121146734651</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,25 +3786,25 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>175.7104291088556</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>199.7865644537354</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>336.1997488099172</v>
       </c>
       <c r="V41" t="n">
-        <v>316.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>325.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>279.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>198.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -3835,7 +3835,7 @@
         <v>17.77625699774189</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>97.22641872844413</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>322.5525556434649</v>
+        <v>225.3261369150208</v>
       </c>
       <c r="S42" t="n">
         <v>150.8871603419698</v>
@@ -3932,19 +3932,19 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>249.5616776741938</v>
+        <v>310.3682526036051</v>
       </c>
       <c r="P43" t="n">
         <v>337</v>
       </c>
       <c r="Q43" t="n">
-        <v>337</v>
+        <v>323.4613473963948</v>
       </c>
       <c r="R43" t="n">
         <v>337</v>
       </c>
       <c r="S43" t="n">
-        <v>47.26792232580625</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3972,13 +3972,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>174.9993129555745</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>103.3391557398498</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -4026,13 +4026,13 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>31.3232663915609</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>322.8510241668239</v>
+        <v>208.5183891801541</v>
       </c>
       <c r="W44" t="n">
         <v>331.3734759809475</v>
@@ -4041,7 +4041,7 @@
         <v>285.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>204.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -4072,7 +4072,7 @@
         <v>23.77625699774189</v>
       </c>
       <c r="I45" t="n">
-        <v>7.226418728444097</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>231.3261369150208</v>
+        <v>238.552555643465</v>
       </c>
       <c r="S45" t="n">
         <v>156.8871603419698</v>
@@ -4160,25 +4160,25 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>98.58503799384475</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>245.6963703536521</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>316.3682526036051</v>
+        <v>109.1868890743212</v>
       </c>
       <c r="P46" t="n">
-        <v>319.7073041109088</v>
+        <v>337</v>
       </c>
       <c r="Q46" t="n">
         <v>337</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73.95649897256939</v>
+        <v>70.58361438686254</v>
       </c>
       <c r="C2" t="n">
-        <v>31.05288458570686</v>
+        <v>27.68</v>
       </c>
       <c r="D2" t="n">
         <v>27.68</v>
@@ -4333,7 +4333,7 @@
         <v>446.2191807537689</v>
       </c>
       <c r="N2" t="n">
-        <v>660.8591164251993</v>
+        <v>788.759180753769</v>
       </c>
       <c r="O2" t="n">
         <v>1003.399116425199</v>
@@ -4351,22 +4351,22 @@
         <v>1301.464213021358</v>
       </c>
       <c r="T2" t="n">
-        <v>1145.69672933291</v>
+        <v>1142.323844747203</v>
       </c>
       <c r="U2" t="n">
-        <v>901.0505184138018</v>
+        <v>897.6776338280949</v>
       </c>
       <c r="V2" t="n">
-        <v>675.9484738008483</v>
+        <v>672.5755892151415</v>
       </c>
       <c r="W2" t="n">
-        <v>442.2378920019114</v>
+        <v>438.8650074162045</v>
       </c>
       <c r="X2" t="n">
-        <v>255.0845248699238</v>
+        <v>251.711640284217</v>
       </c>
       <c r="Y2" t="n">
-        <v>149.713380745877</v>
+        <v>146.3404961601701</v>
       </c>
     </row>
     <row r="3">
@@ -4376,34 +4376,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>904.989366771433</v>
+        <v>991.4311238728238</v>
       </c>
       <c r="C3" t="n">
-        <v>904.989366771433</v>
+        <v>991.4311238728238</v>
       </c>
       <c r="D3" t="n">
-        <v>904.989366771433</v>
+        <v>991.4311238728238</v>
       </c>
       <c r="E3" t="n">
-        <v>904.989366771433</v>
+        <v>991.4311238728238</v>
       </c>
       <c r="F3" t="n">
-        <v>904.989366771433</v>
+        <v>690.6816966315375</v>
       </c>
       <c r="G3" t="n">
-        <v>576.1051014507459</v>
+        <v>361.7974313108504</v>
       </c>
       <c r="H3" t="n">
-        <v>241.9876701398956</v>
+        <v>27.68</v>
       </c>
       <c r="I3" t="n">
-        <v>27.67999999997801</v>
+        <v>27.68</v>
       </c>
       <c r="J3" t="n">
-        <v>165.1159025337675</v>
+        <v>165.1159025337895</v>
       </c>
       <c r="K3" t="n">
-        <v>377.3471300432452</v>
+        <v>377.3471300432673</v>
       </c>
       <c r="L3" t="n">
         <v>678.6214735340828</v>
@@ -4442,10 +4442,10 @@
         <v>1004.423789979276</v>
       </c>
       <c r="X3" t="n">
-        <v>904.989366771433</v>
+        <v>991.4311238728238</v>
       </c>
       <c r="Y3" t="n">
-        <v>904.989366771433</v>
+        <v>991.4311238728238</v>
       </c>
     </row>
     <row r="4">
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>728.7006130558991</v>
+        <v>468.9321862669697</v>
       </c>
       <c r="C4" t="n">
-        <v>728.7006130558991</v>
+        <v>601.8641920854055</v>
       </c>
       <c r="D4" t="n">
-        <v>728.7006130558991</v>
+        <v>722.1133362104056</v>
       </c>
       <c r="E4" t="n">
-        <v>728.7006130558991</v>
+        <v>846.8722404218186</v>
       </c>
       <c r="F4" t="n">
-        <v>728.7006130558991</v>
+        <v>978.1632130137541</v>
       </c>
       <c r="G4" t="n">
-        <v>843.6389252463396</v>
+        <v>1138.619390376049</v>
       </c>
       <c r="H4" t="n">
-        <v>1021.148965159835</v>
+        <v>1316.129430289545</v>
       </c>
       <c r="I4" t="n">
-        <v>1252.808887374607</v>
+        <v>1382.599187613906</v>
       </c>
       <c r="J4" t="n">
-        <v>1252.808887374607</v>
+        <v>1382.599187613906</v>
       </c>
       <c r="K4" t="n">
-        <v>1384</v>
+        <v>1382.599187613906</v>
       </c>
       <c r="L4" t="n">
         <v>1384</v>
@@ -4509,22 +4509,22 @@
         <v>73.94475689745182</v>
       </c>
       <c r="T4" t="n">
-        <v>269.4615032693715</v>
+        <v>73.94475689745182</v>
       </c>
       <c r="U4" t="n">
-        <v>522.9492201699532</v>
+        <v>73.94475689745182</v>
       </c>
       <c r="V4" t="n">
-        <v>728.7006130558991</v>
+        <v>73.94475689745182</v>
       </c>
       <c r="W4" t="n">
-        <v>728.7006130558991</v>
+        <v>73.94475689745182</v>
       </c>
       <c r="X4" t="n">
-        <v>728.7006130558991</v>
+        <v>231.9055479216453</v>
       </c>
       <c r="Y4" t="n">
-        <v>728.7006130558991</v>
+        <v>350.2448486006776</v>
       </c>
     </row>
     <row r="5">
@@ -4558,25 +4558,25 @@
         <v>27.68</v>
       </c>
       <c r="J5" t="n">
-        <v>370.22</v>
+        <v>27.68</v>
       </c>
       <c r="K5" t="n">
-        <v>404.1392954271357</v>
+        <v>61.59929542713568</v>
       </c>
       <c r="L5" t="n">
+        <v>103.6791807537689</v>
+      </c>
+      <c r="M5" t="n">
         <v>446.2191807537689</v>
       </c>
-      <c r="M5" t="n">
-        <v>660.8591164251993</v>
-      </c>
       <c r="N5" t="n">
-        <v>1003.399116425199</v>
+        <v>446.2191807537689</v>
       </c>
       <c r="O5" t="n">
-        <v>1003.399116425199</v>
+        <v>788.759180753769</v>
       </c>
       <c r="P5" t="n">
-        <v>1041.46</v>
+        <v>1131.299180753769</v>
       </c>
       <c r="Q5" t="n">
         <v>1384</v>
@@ -4588,13 +4588,13 @@
         <v>1301.464213021358</v>
       </c>
       <c r="T5" t="n">
-        <v>1121.164701504256</v>
+        <v>1145.69672933291</v>
       </c>
       <c r="U5" t="n">
-        <v>876.518490585148</v>
+        <v>901.0505184138018</v>
       </c>
       <c r="V5" t="n">
-        <v>651.4164459721945</v>
+        <v>675.9484738008483</v>
       </c>
       <c r="W5" t="n">
         <v>442.2378920019114</v>
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>241.9876701399176</v>
+        <v>654.9288404843431</v>
       </c>
       <c r="C6" t="n">
-        <v>241.9876701399176</v>
+        <v>654.9288404843431</v>
       </c>
       <c r="D6" t="n">
-        <v>241.9876701399176</v>
+        <v>373.8134315372855</v>
       </c>
       <c r="E6" t="n">
-        <v>241.9876701399176</v>
+        <v>27.68</v>
       </c>
       <c r="F6" t="n">
-        <v>241.9876701399176</v>
+        <v>27.68</v>
       </c>
       <c r="G6" t="n">
-        <v>241.9876701399176</v>
+        <v>27.68</v>
       </c>
       <c r="H6" t="n">
-        <v>241.9876701399176</v>
+        <v>27.68</v>
       </c>
       <c r="I6" t="n">
         <v>27.68</v>
@@ -4661,28 +4661,28 @@
         <v>1227.754201452363</v>
       </c>
       <c r="R6" t="n">
-        <v>878.2592519574131</v>
+        <v>1095.101537901837</v>
       </c>
       <c r="S6" t="n">
-        <v>528.7643024624635</v>
+        <v>1037.639759778635</v>
       </c>
       <c r="T6" t="n">
-        <v>528.7643024624635</v>
+        <v>1037.639759778635</v>
       </c>
       <c r="U6" t="n">
-        <v>528.7643024624635</v>
+        <v>1037.639759778635</v>
       </c>
       <c r="V6" t="n">
-        <v>280.6097735290247</v>
+        <v>1030.053227261948</v>
       </c>
       <c r="W6" t="n">
-        <v>254.9803362463696</v>
+        <v>1004.423789979293</v>
       </c>
       <c r="X6" t="n">
-        <v>241.9876701399176</v>
+        <v>654.9288404843431</v>
       </c>
       <c r="Y6" t="n">
-        <v>241.9876701399176</v>
+        <v>654.9288404843431</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>422.6674293695179</v>
+        <v>465.9390919318975</v>
       </c>
       <c r="C7" t="n">
-        <v>555.5994351879538</v>
+        <v>465.9390919318975</v>
       </c>
       <c r="D7" t="n">
-        <v>675.8485793129538</v>
+        <v>586.1882360568975</v>
       </c>
       <c r="E7" t="n">
-        <v>800.6074835243668</v>
+        <v>710.9471402683105</v>
       </c>
       <c r="F7" t="n">
-        <v>931.8984561163022</v>
+        <v>842.238112860246</v>
       </c>
       <c r="G7" t="n">
-        <v>1092.354633478597</v>
+        <v>842.238112860246</v>
       </c>
       <c r="H7" t="n">
-        <v>1269.864673392093</v>
+        <v>1019.748152773742</v>
       </c>
       <c r="I7" t="n">
-        <v>1384</v>
+        <v>1251.408074988513</v>
       </c>
       <c r="J7" t="n">
-        <v>1384</v>
+        <v>1251.408074988513</v>
       </c>
       <c r="K7" t="n">
-        <v>1384</v>
+        <v>1382.599187613906</v>
       </c>
       <c r="L7" t="n">
         <v>1384</v>
@@ -4731,10 +4731,10 @@
         <v>1141.182879828973</v>
       </c>
       <c r="O7" t="n">
-        <v>925.3842522907206</v>
+        <v>922.629089320281</v>
       </c>
       <c r="P7" t="n">
-        <v>656.8637400035054</v>
+        <v>654.1085770330658</v>
       </c>
       <c r="Q7" t="n">
         <v>345.0230668463357</v>
@@ -4743,25 +4743,25 @@
         <v>27.68</v>
       </c>
       <c r="S7" t="n">
-        <v>27.68</v>
+        <v>73.94475689745181</v>
       </c>
       <c r="T7" t="n">
-        <v>27.68</v>
+        <v>73.94475689745181</v>
       </c>
       <c r="U7" t="n">
-        <v>27.68</v>
+        <v>327.4324737980336</v>
       </c>
       <c r="V7" t="n">
-        <v>27.68</v>
+        <v>347.2517542656053</v>
       </c>
       <c r="W7" t="n">
-        <v>27.68</v>
+        <v>347.2517542656053</v>
       </c>
       <c r="X7" t="n">
-        <v>185.6407910241935</v>
+        <v>347.2517542656053</v>
       </c>
       <c r="Y7" t="n">
-        <v>303.9800917032258</v>
+        <v>347.2517542656053</v>
       </c>
     </row>
     <row r="8">
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>74.4364989725694</v>
+        <v>73.42447114391554</v>
       </c>
       <c r="C8" t="n">
-        <v>31.53288458570686</v>
+        <v>30.520856757053</v>
       </c>
       <c r="D8" t="n">
         <v>28.16</v>
@@ -4798,22 +4798,22 @@
         <v>28.16</v>
       </c>
       <c r="K8" t="n">
-        <v>376.64</v>
+        <v>62.07929542713568</v>
       </c>
       <c r="L8" t="n">
-        <v>672.9791164251992</v>
+        <v>324.4991164251787</v>
       </c>
       <c r="M8" t="n">
-        <v>1021.459116425199</v>
+        <v>672.9791164251856</v>
       </c>
       <c r="N8" t="n">
-        <v>1369.939116425199</v>
+        <v>1021.459116425192</v>
       </c>
       <c r="O8" t="n">
-        <v>1369.939116425199</v>
+        <v>1021.459116425192</v>
       </c>
       <c r="P8" t="n">
-        <v>1408</v>
+        <v>1059.519999999993</v>
       </c>
       <c r="Q8" t="n">
         <v>1408</v>
@@ -4834,13 +4834,13 @@
         <v>675.4164459721945</v>
       </c>
       <c r="W8" t="n">
-        <v>442.7178920019114</v>
+        <v>441.7058641732576</v>
       </c>
       <c r="X8" t="n">
-        <v>255.5645248699238</v>
+        <v>254.55249704127</v>
       </c>
       <c r="Y8" t="n">
-        <v>150.193380745877</v>
+        <v>149.1813529172231</v>
       </c>
     </row>
     <row r="9">
@@ -4895,25 +4895,25 @@
         <v>1385.534105368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1229.288306820881</v>
+        <v>1385.534105368536</v>
       </c>
       <c r="R9" t="n">
-        <v>873.7327512653258</v>
+        <v>1029.978549812969</v>
       </c>
       <c r="S9" t="n">
-        <v>518.1771957097701</v>
+        <v>972.5167716897674</v>
       </c>
       <c r="T9" t="n">
-        <v>162.6216401542145</v>
+        <v>972.5167716897674</v>
       </c>
       <c r="U9" t="n">
-        <v>162.6216401542145</v>
+        <v>616.9612161342048</v>
       </c>
       <c r="V9" t="n">
-        <v>155.0351076375275</v>
+        <v>609.3746836175178</v>
       </c>
       <c r="W9" t="n">
-        <v>129.4056703548724</v>
+        <v>253.8191280619552</v>
       </c>
       <c r="X9" t="n">
         <v>28.16</v>
@@ -4929,19 +4929,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1009.295108815591</v>
+        <v>807.7197405151413</v>
       </c>
       <c r="C10" t="n">
-        <v>1142.227114634027</v>
+        <v>940.6517463335771</v>
       </c>
       <c r="D10" t="n">
-        <v>1262.476258759027</v>
+        <v>1060.900890458577</v>
       </c>
       <c r="E10" t="n">
-        <v>1387.23516297044</v>
+        <v>1185.65979466999</v>
       </c>
       <c r="F10" t="n">
-        <v>1387.23516297044</v>
+        <v>1316.950767261926</v>
       </c>
       <c r="G10" t="n">
         <v>1387.23516297044</v>
@@ -4986,19 +4986,19 @@
         <v>28.16</v>
       </c>
       <c r="U10" t="n">
-        <v>229.7353683004495</v>
+        <v>28.16</v>
       </c>
       <c r="V10" t="n">
-        <v>435.4867611863954</v>
+        <v>233.911392885946</v>
       </c>
       <c r="W10" t="n">
-        <v>614.3076794460728</v>
+        <v>412.7323111456234</v>
       </c>
       <c r="X10" t="n">
-        <v>772.2684704702664</v>
+        <v>570.6931021698169</v>
       </c>
       <c r="Y10" t="n">
-        <v>890.6077711492986</v>
+        <v>689.0324028488492</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>102.0075533849213</v>
+        <v>107.3118073923433</v>
       </c>
       <c r="C11" t="n">
-        <v>52.03323192735167</v>
+        <v>57.33748593477365</v>
       </c>
       <c r="D11" t="n">
-        <v>41.58964027093774</v>
+        <v>46.89389427835972</v>
       </c>
       <c r="E11" t="n">
-        <v>37.18227703167648</v>
+        <v>42.48653103909846</v>
       </c>
       <c r="F11" t="n">
-        <v>32.24325813469481</v>
+        <v>37.54751214211679</v>
       </c>
       <c r="G11" t="n">
-        <v>28.72</v>
+        <v>34.02425400742196</v>
       </c>
       <c r="H11" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="I11" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="J11" t="n">
-        <v>28.72</v>
+        <v>384.1300000000176</v>
       </c>
       <c r="K11" t="n">
-        <v>384.13</v>
+        <v>645.0392310985973</v>
       </c>
       <c r="L11" t="n">
-        <v>687.1191164251991</v>
+        <v>687.1191164252305</v>
       </c>
       <c r="M11" t="n">
-        <v>1042.529116425199</v>
+        <v>1042.529116425247</v>
       </c>
       <c r="N11" t="n">
-        <v>1397.939116425199</v>
+        <v>1397.939116425263</v>
       </c>
       <c r="O11" t="n">
-        <v>1397.939116425199</v>
+        <v>1397.939116425263</v>
       </c>
       <c r="P11" t="n">
-        <v>1436</v>
+        <v>1436.000000000064</v>
       </c>
       <c r="Q11" t="n">
-        <v>1436</v>
+        <v>1436.000000000064</v>
       </c>
       <c r="R11" t="n">
-        <v>1436</v>
+        <v>1436.000000000064</v>
       </c>
       <c r="S11" t="n">
-        <v>1346.393505950651</v>
+        <v>1346.393505950715</v>
       </c>
       <c r="T11" t="n">
-        <v>1216.172026169505</v>
+        <v>1159.023287362906</v>
       </c>
       <c r="U11" t="n">
-        <v>964.4551081796891</v>
+        <v>907.3063693730903</v>
       </c>
       <c r="V11" t="n">
-        <v>732.2823564960286</v>
+        <v>675.1336176894298</v>
       </c>
       <c r="W11" t="n">
-        <v>491.5010676263846</v>
+        <v>434.3523288197858</v>
       </c>
       <c r="X11" t="n">
-        <v>297.2769934236899</v>
+        <v>240.1282546170911</v>
       </c>
       <c r="Y11" t="n">
-        <v>184.835142228936</v>
+        <v>127.6864034223372</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1034.788608083938</v>
+        <v>391.3462626262805</v>
       </c>
       <c r="C12" t="n">
-        <v>1034.788608083938</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="D12" t="n">
-        <v>1034.788608083938</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="E12" t="n">
-        <v>1034.788608083938</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="F12" t="n">
-        <v>691.7216966315375</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="G12" t="n">
-        <v>362.8374313108504</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="H12" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="I12" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="J12" t="n">
-        <v>166.1559025337895</v>
+        <v>166.1559025337908</v>
       </c>
       <c r="K12" t="n">
-        <v>378.3871300432672</v>
+        <v>378.3871300432685</v>
       </c>
       <c r="L12" t="n">
-        <v>680.7155789026183</v>
+        <v>680.7155789026195</v>
       </c>
       <c r="M12" t="n">
-        <v>802.9459706454775</v>
+        <v>802.9459706454787</v>
       </c>
       <c r="N12" t="n">
-        <v>973.3328842153099</v>
+        <v>973.3328842153112</v>
       </c>
       <c r="O12" t="n">
-        <v>1246.320652031104</v>
+        <v>1246.320652031106</v>
       </c>
       <c r="P12" t="n">
-        <v>1386.094105368536</v>
+        <v>1386.094105368537</v>
       </c>
       <c r="Q12" t="n">
-        <v>1386.094105368536</v>
+        <v>1229.848306820882</v>
       </c>
       <c r="R12" t="n">
-        <v>1246.370734747302</v>
+        <v>1090.124936199649</v>
       </c>
       <c r="S12" t="n">
-        <v>1107.237412158555</v>
+        <v>806.3579561500176</v>
       </c>
       <c r="T12" t="n">
-        <v>1102.412272907017</v>
+        <v>801.5328168984789</v>
       </c>
       <c r="U12" t="n">
-        <v>1102.209365201854</v>
+        <v>801.329909193316</v>
       </c>
       <c r="V12" t="n">
-        <v>1087.55212561446</v>
+        <v>786.6726696059219</v>
       </c>
       <c r="W12" t="n">
-        <v>1054.851981261098</v>
+        <v>753.9725252525598</v>
       </c>
       <c r="X12" t="n">
-        <v>1034.788608083938</v>
+        <v>391.3462626262805</v>
       </c>
       <c r="Y12" t="n">
-        <v>1034.788608083938</v>
+        <v>391.3462626262805</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>874.1743838875332</v>
+        <v>451.8326189644745</v>
       </c>
       <c r="C13" t="n">
-        <v>874.1743838875332</v>
+        <v>577.8346247829103</v>
       </c>
       <c r="D13" t="n">
-        <v>987.4935280125333</v>
+        <v>691.1537689079104</v>
       </c>
       <c r="E13" t="n">
-        <v>987.4935280125333</v>
+        <v>808.9826731193234</v>
       </c>
       <c r="F13" t="n">
-        <v>987.4935280125333</v>
+        <v>933.3436457112589</v>
       </c>
       <c r="G13" t="n">
-        <v>1141.019705374828</v>
+        <v>1086.869823073554</v>
       </c>
       <c r="H13" t="n">
-        <v>1311.599745288324</v>
+        <v>1086.869823073554</v>
       </c>
       <c r="I13" t="n">
-        <v>1311.599745288324</v>
+        <v>1311.599745288325</v>
       </c>
       <c r="J13" t="n">
-        <v>1311.599745288324</v>
+        <v>1311.599745288325</v>
       </c>
       <c r="K13" t="n">
-        <v>1435.860857913717</v>
+        <v>1435.860857913719</v>
       </c>
       <c r="L13" t="n">
-        <v>1430.219405394682</v>
+        <v>1430.219405394683</v>
       </c>
       <c r="M13" t="n">
-        <v>1327.499629015223</v>
+        <v>1327.499629015224</v>
       </c>
       <c r="N13" t="n">
-        <v>1173.260871082241</v>
+        <v>1173.260871082242</v>
       </c>
       <c r="O13" t="n">
-        <v>947.6363735028419</v>
+        <v>947.6363735028431</v>
       </c>
       <c r="P13" t="n">
-        <v>672.0451541449196</v>
+        <v>672.0451541449208</v>
       </c>
       <c r="Q13" t="n">
-        <v>353.1337739170428</v>
+        <v>353.1337739170441</v>
       </c>
       <c r="R13" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="S13" t="n">
-        <v>68.05475689745181</v>
+        <v>68.0547568974531</v>
       </c>
       <c r="T13" t="n">
-        <v>256.6415032693714</v>
+        <v>228.6659806191501</v>
       </c>
       <c r="U13" t="n">
-        <v>503.1992201699532</v>
+        <v>228.6659806191501</v>
       </c>
       <c r="V13" t="n">
-        <v>702.020613055899</v>
+        <v>228.6659806191501</v>
       </c>
       <c r="W13" t="n">
-        <v>873.9115313155764</v>
+        <v>228.6659806191501</v>
       </c>
       <c r="X13" t="n">
-        <v>874.1743838875332</v>
+        <v>228.6659806191501</v>
       </c>
       <c r="Y13" t="n">
-        <v>874.1743838875332</v>
+        <v>340.0752812981823</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>97.96542525609907</v>
+        <v>52.9301226955124</v>
       </c>
       <c r="C14" t="n">
-        <v>47.99110379852945</v>
+        <v>52.9301226955124</v>
       </c>
       <c r="D14" t="n">
-        <v>37.54751214211552</v>
+        <v>42.48653103909847</v>
       </c>
       <c r="E14" t="n">
-        <v>37.54751214211552</v>
+        <v>42.48653103909847</v>
       </c>
       <c r="F14" t="n">
-        <v>37.54751214211552</v>
+        <v>37.5475121421168</v>
       </c>
       <c r="G14" t="n">
-        <v>34.02425400742071</v>
+        <v>34.02425400742199</v>
       </c>
       <c r="H14" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="I14" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="J14" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="K14" t="n">
-        <v>289.6292310985659</v>
+        <v>384.130000000017</v>
       </c>
       <c r="L14" t="n">
-        <v>331.7091164251991</v>
+        <v>426.2098853266502</v>
       </c>
       <c r="M14" t="n">
-        <v>687.1191164251991</v>
+        <v>781.6198853266601</v>
       </c>
       <c r="N14" t="n">
-        <v>1042.529116425199</v>
+        <v>1137.02988532667</v>
       </c>
       <c r="O14" t="n">
-        <v>1042.529116425199</v>
+        <v>1137.02988532667</v>
       </c>
       <c r="P14" t="n">
-        <v>1080.59</v>
+        <v>1175.090768901471</v>
       </c>
       <c r="Q14" t="n">
-        <v>1436</v>
+        <v>1436.000000000062</v>
       </c>
       <c r="R14" t="n">
-        <v>1436</v>
+        <v>1436.000000000062</v>
       </c>
       <c r="S14" t="n">
-        <v>1346.393505950651</v>
+        <v>1346.393505950713</v>
       </c>
       <c r="T14" t="n">
-        <v>1159.023287362842</v>
+        <v>1159.023287362904</v>
       </c>
       <c r="U14" t="n">
-        <v>907.3063693730269</v>
+        <v>907.306369373089</v>
       </c>
       <c r="V14" t="n">
-        <v>675.1336176893664</v>
+        <v>675.1336176894284</v>
       </c>
       <c r="W14" t="n">
-        <v>434.3523288197223</v>
+        <v>434.3523288197844</v>
       </c>
       <c r="X14" t="n">
-        <v>240.1282546170277</v>
+        <v>240.1282546170897</v>
       </c>
       <c r="Y14" t="n">
-        <v>127.6864034222737</v>
+        <v>127.6864034223358</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>937.5467905798969</v>
+        <v>384.1369202262322</v>
       </c>
       <c r="C15" t="n">
-        <v>937.5467905798969</v>
+        <v>384.1369202262322</v>
       </c>
       <c r="D15" t="n">
-        <v>586.0945815923185</v>
+        <v>384.1369202262322</v>
       </c>
       <c r="E15" t="n">
-        <v>586.0945815923185</v>
+        <v>38.00348868894667</v>
       </c>
       <c r="F15" t="n">
-        <v>243.0276701399175</v>
+        <v>38.00348868894667</v>
       </c>
       <c r="G15" t="n">
-        <v>243.0276701399175</v>
+        <v>38.00348868894667</v>
       </c>
       <c r="H15" t="n">
-        <v>243.0276701399175</v>
+        <v>38.00348868894667</v>
       </c>
       <c r="I15" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="J15" t="n">
-        <v>166.1559025337895</v>
+        <v>166.1559025337908</v>
       </c>
       <c r="K15" t="n">
-        <v>378.3871300432672</v>
+        <v>378.3871300432685</v>
       </c>
       <c r="L15" t="n">
-        <v>680.7155789026183</v>
+        <v>680.7155789026195</v>
       </c>
       <c r="M15" t="n">
-        <v>802.9459706454775</v>
+        <v>802.9459706454787</v>
       </c>
       <c r="N15" t="n">
-        <v>973.3328842153099</v>
+        <v>973.3328842153112</v>
       </c>
       <c r="O15" t="n">
-        <v>1246.320652031104</v>
+        <v>1246.320652031106</v>
       </c>
       <c r="P15" t="n">
-        <v>1386.094105368536</v>
+        <v>1386.094105368537</v>
       </c>
       <c r="Q15" t="n">
-        <v>1386.094105368536</v>
+        <v>1386.094105368537</v>
       </c>
       <c r="R15" t="n">
-        <v>1246.370734747302</v>
+        <v>1246.370734747303</v>
       </c>
       <c r="S15" t="n">
-        <v>1181.838249553393</v>
+        <v>1181.838249553395</v>
       </c>
       <c r="T15" t="n">
-        <v>1177.013110301855</v>
+        <v>1177.013110301856</v>
       </c>
       <c r="U15" t="n">
-        <v>1176.810202596692</v>
+        <v>1176.810202596693</v>
       </c>
       <c r="V15" t="n">
-        <v>1162.152963009298</v>
+        <v>1162.152963009299</v>
       </c>
       <c r="W15" t="n">
-        <v>1129.452818655936</v>
+        <v>1129.452818655937</v>
       </c>
       <c r="X15" t="n">
-        <v>1109.389445478776</v>
+        <v>1109.389445478778</v>
       </c>
       <c r="Y15" t="n">
-        <v>1109.389445478776</v>
+        <v>746.763182852505</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>314.6124737980335</v>
+        <v>654.2300111941479</v>
       </c>
       <c r="C16" t="n">
-        <v>314.6124737980335</v>
+        <v>654.2300111941479</v>
       </c>
       <c r="D16" t="n">
-        <v>427.9316179230336</v>
+        <v>654.2300111941479</v>
       </c>
       <c r="E16" t="n">
-        <v>427.9316179230336</v>
+        <v>654.2300111941479</v>
       </c>
       <c r="F16" t="n">
-        <v>427.9316179230336</v>
+        <v>762.7636057977629</v>
       </c>
       <c r="G16" t="n">
-        <v>581.4577952853288</v>
+        <v>916.2897831600581</v>
       </c>
       <c r="H16" t="n">
-        <v>752.0378351988247</v>
+        <v>1086.869823073554</v>
       </c>
       <c r="I16" t="n">
-        <v>976.7677574135962</v>
+        <v>1311.599745288325</v>
       </c>
       <c r="J16" t="n">
-        <v>1332.177757413596</v>
+        <v>1311.599745288325</v>
       </c>
       <c r="K16" t="n">
-        <v>1435.860857913717</v>
+        <v>1435.860857913719</v>
       </c>
       <c r="L16" t="n">
-        <v>1430.219405394682</v>
+        <v>1430.219405394683</v>
       </c>
       <c r="M16" t="n">
-        <v>1327.499629015223</v>
+        <v>1327.499629015224</v>
       </c>
       <c r="N16" t="n">
-        <v>1173.260871082241</v>
+        <v>1173.260871082242</v>
       </c>
       <c r="O16" t="n">
-        <v>947.6363735028419</v>
+        <v>947.6363735028431</v>
       </c>
       <c r="P16" t="n">
-        <v>672.0451541449196</v>
+        <v>672.0451541449208</v>
       </c>
       <c r="Q16" t="n">
-        <v>353.1337739170428</v>
+        <v>353.1337739170441</v>
       </c>
       <c r="R16" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="S16" t="n">
-        <v>68.05475689745181</v>
+        <v>68.05475689745309</v>
       </c>
       <c r="T16" t="n">
-        <v>68.05475689745181</v>
+        <v>256.6415032693727</v>
       </c>
       <c r="U16" t="n">
-        <v>314.6124737980335</v>
+        <v>503.1992201699544</v>
       </c>
       <c r="V16" t="n">
-        <v>314.6124737980335</v>
+        <v>503.1992201699544</v>
       </c>
       <c r="W16" t="n">
-        <v>314.6124737980335</v>
+        <v>503.1992201699544</v>
       </c>
       <c r="X16" t="n">
-        <v>314.6124737980335</v>
+        <v>654.2300111941479</v>
       </c>
       <c r="Y16" t="n">
-        <v>314.6124737980335</v>
+        <v>654.2300111941479</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>83.07967435343102</v>
+        <v>83.07967435343767</v>
       </c>
       <c r="C17" t="n">
-        <v>37.14575693626544</v>
+        <v>37.14575693627209</v>
       </c>
       <c r="D17" t="n">
-        <v>30.74256932025555</v>
+        <v>30.74256932026221</v>
       </c>
       <c r="E17" t="n">
-        <v>30.37561012139833</v>
+        <v>30.37561012140499</v>
       </c>
       <c r="F17" t="n">
-        <v>29.4769952648207</v>
+        <v>29.47699526482736</v>
       </c>
       <c r="G17" t="n">
-        <v>29.98384996701667</v>
+        <v>29.98384996701792</v>
       </c>
       <c r="H17" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="I17" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="J17" t="n">
-        <v>384.13</v>
+        <v>384.1300000000113</v>
       </c>
       <c r="K17" t="n">
-        <v>418.0492954271357</v>
+        <v>418.0492954271469</v>
       </c>
       <c r="L17" t="n">
-        <v>460.1291807537689</v>
+        <v>687.1191164252413</v>
       </c>
       <c r="M17" t="n">
-        <v>815.539180753769</v>
+        <v>1042.529116425251</v>
       </c>
       <c r="N17" t="n">
-        <v>1042.529116425199</v>
+        <v>1042.529116425251</v>
       </c>
       <c r="O17" t="n">
-        <v>1042.529116425199</v>
+        <v>1042.529116425251</v>
       </c>
       <c r="P17" t="n">
-        <v>1080.59</v>
+        <v>1080.590000000052</v>
       </c>
       <c r="Q17" t="n">
-        <v>1436</v>
+        <v>1436.000000000062</v>
       </c>
       <c r="R17" t="n">
-        <v>1436</v>
+        <v>1436.000000000062</v>
       </c>
       <c r="S17" t="n">
-        <v>1356.331537442995</v>
+        <v>1356.331537443001</v>
       </c>
       <c r="T17" t="n">
-        <v>1173.00172289559</v>
+        <v>1173.001722895597</v>
       </c>
       <c r="U17" t="n">
-        <v>925.3252089461787</v>
+        <v>925.3252089461853</v>
       </c>
       <c r="V17" t="n">
-        <v>697.1928613029222</v>
+        <v>697.1928613029288</v>
       </c>
       <c r="W17" t="n">
-        <v>460.4519764736822</v>
+        <v>460.4519764736888</v>
       </c>
       <c r="X17" t="n">
-        <v>270.2683063113915</v>
+        <v>270.2683063113982</v>
       </c>
       <c r="Y17" t="n">
-        <v>161.8668591570416</v>
+        <v>161.8668591570483</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="C18" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="D18" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="E18" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="F18" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="G18" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="H18" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="I18" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="J18" t="n">
-        <v>166.1559025337895</v>
+        <v>166.1559025337908</v>
       </c>
       <c r="K18" t="n">
-        <v>378.3871300432672</v>
+        <v>378.3871300432685</v>
       </c>
       <c r="L18" t="n">
-        <v>680.7155789026183</v>
+        <v>680.7155789026195</v>
       </c>
       <c r="M18" t="n">
-        <v>802.9459706454775</v>
+        <v>802.9459706454787</v>
       </c>
       <c r="N18" t="n">
-        <v>973.3328842153099</v>
+        <v>973.3328842153112</v>
       </c>
       <c r="O18" t="n">
-        <v>1246.320652031104</v>
+        <v>1246.320652031106</v>
       </c>
       <c r="P18" t="n">
-        <v>1386.094105368536</v>
+        <v>1386.094105368537</v>
       </c>
       <c r="Q18" t="n">
-        <v>1386.094105368536</v>
+        <v>1229.848306820882</v>
       </c>
       <c r="R18" t="n">
-        <v>1250.411138787706</v>
+        <v>1094.165340240053</v>
       </c>
       <c r="S18" t="n">
-        <v>1189.919057634202</v>
+        <v>1033.673259086549</v>
       </c>
       <c r="T18" t="n">
-        <v>1189.134322423067</v>
+        <v>1032.888523875414</v>
       </c>
       <c r="U18" t="n">
-        <v>1189.134322423067</v>
+        <v>769.9954943893019</v>
       </c>
       <c r="V18" t="n">
-        <v>1178.517486876077</v>
+        <v>407.3692317630292</v>
       </c>
       <c r="W18" t="n">
-        <v>1116.598787878788</v>
+        <v>44.74296913675637</v>
       </c>
       <c r="X18" t="n">
-        <v>753.9725252525252</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="Y18" t="n">
-        <v>391.3462626262626</v>
+        <v>28.72000000000127</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>524.1507632735804</v>
+        <v>812.8608190703999</v>
       </c>
       <c r="C19" t="n">
-        <v>654.1127690920162</v>
+        <v>942.8228248888356</v>
       </c>
       <c r="D19" t="n">
-        <v>771.3919132170162</v>
+        <v>1060.101969013836</v>
       </c>
       <c r="E19" t="n">
-        <v>893.1808174284292</v>
+        <v>1181.890873225249</v>
       </c>
       <c r="F19" t="n">
-        <v>893.1808174284292</v>
+        <v>1310.211845817184</v>
       </c>
       <c r="G19" t="n">
-        <v>1050.666994790724</v>
+        <v>1310.211845817184</v>
       </c>
       <c r="H19" t="n">
-        <v>1050.666994790724</v>
+        <v>1407.57802963089</v>
       </c>
       <c r="I19" t="n">
-        <v>1279.356917005496</v>
+        <v>1407.57802963089</v>
       </c>
       <c r="J19" t="n">
-        <v>1279.356917005496</v>
+        <v>1407.57802963089</v>
       </c>
       <c r="K19" t="n">
-        <v>1407.578029630889</v>
+        <v>1407.57802963089</v>
       </c>
       <c r="L19" t="n">
-        <v>1405.976981152258</v>
+        <v>1405.976981152259</v>
       </c>
       <c r="M19" t="n">
-        <v>1307.297608813203</v>
+        <v>1307.297608813204</v>
       </c>
       <c r="N19" t="n">
-        <v>1157.099254920625</v>
+        <v>1157.099254920626</v>
       </c>
       <c r="O19" t="n">
-        <v>935.5151613816297</v>
+        <v>935.5151613816311</v>
       </c>
       <c r="P19" t="n">
-        <v>663.9643460641115</v>
+        <v>663.9643460641128</v>
       </c>
       <c r="Q19" t="n">
-        <v>349.0933698766388</v>
+        <v>349.0933698766401</v>
       </c>
       <c r="R19" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="S19" t="n">
-        <v>72.0147568974518</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="T19" t="n">
-        <v>72.0147568974518</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="U19" t="n">
-        <v>205.6520327213424</v>
+        <v>279.237716900583</v>
       </c>
       <c r="V19" t="n">
-        <v>408.4334256072883</v>
+        <v>482.0191097865289</v>
       </c>
       <c r="W19" t="n">
-        <v>408.4334256072883</v>
+        <v>657.8700280462064</v>
       </c>
       <c r="X19" t="n">
-        <v>408.4334256072883</v>
+        <v>812.8608190703999</v>
       </c>
       <c r="Y19" t="n">
-        <v>408.4334256072883</v>
+        <v>812.8608190703999</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>83.07967435343302</v>
+        <v>77.18204690155324</v>
       </c>
       <c r="C20" t="n">
-        <v>37.14575693626745</v>
+        <v>31.24812948438766</v>
       </c>
       <c r="D20" t="n">
-        <v>30.74256932025756</v>
+        <v>30.74256932026243</v>
       </c>
       <c r="E20" t="n">
-        <v>30.37561012140034</v>
+        <v>30.37561012140521</v>
       </c>
       <c r="F20" t="n">
-        <v>29.47699526482271</v>
+        <v>29.47699526482758</v>
       </c>
       <c r="G20" t="n">
-        <v>29.98384996701665</v>
+        <v>29.98384996701792</v>
       </c>
       <c r="H20" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="I20" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="J20" t="n">
-        <v>384.13</v>
+        <v>384.1300000000113</v>
       </c>
       <c r="K20" t="n">
-        <v>418.0492954271357</v>
+        <v>683.1001146734088</v>
       </c>
       <c r="L20" t="n">
-        <v>460.1291807537689</v>
+        <v>725.180000000042</v>
       </c>
       <c r="M20" t="n">
-        <v>687.1191164251991</v>
+        <v>725.180000000042</v>
       </c>
       <c r="N20" t="n">
-        <v>1042.529116425199</v>
+        <v>725.180000000042</v>
       </c>
       <c r="O20" t="n">
-        <v>1042.529116425199</v>
+        <v>725.180000000042</v>
       </c>
       <c r="P20" t="n">
-        <v>1080.59</v>
+        <v>1080.590000000052</v>
       </c>
       <c r="Q20" t="n">
-        <v>1436</v>
+        <v>1436.000000000062</v>
       </c>
       <c r="R20" t="n">
-        <v>1436</v>
+        <v>1436.000000000062</v>
       </c>
       <c r="S20" t="n">
-        <v>1356.331537442997</v>
+        <v>1350.433909991117</v>
       </c>
       <c r="T20" t="n">
-        <v>1173.001722895592</v>
+        <v>1167.104095443712</v>
       </c>
       <c r="U20" t="n">
-        <v>925.3252089461806</v>
+        <v>919.4275814943009</v>
       </c>
       <c r="V20" t="n">
-        <v>697.1928613029241</v>
+        <v>691.2952338510444</v>
       </c>
       <c r="W20" t="n">
-        <v>460.4519764736842</v>
+        <v>454.5543490218044</v>
       </c>
       <c r="X20" t="n">
-        <v>270.2683063113935</v>
+        <v>264.3706788595138</v>
       </c>
       <c r="Y20" t="n">
-        <v>161.8668591570436</v>
+        <v>155.9692317051638</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28.72</v>
+        <v>72.59579423129162</v>
       </c>
       <c r="C21" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="D21" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="E21" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="F21" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="G21" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="H21" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="I21" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="J21" t="n">
-        <v>166.1559025337895</v>
+        <v>166.1559025337908</v>
       </c>
       <c r="K21" t="n">
-        <v>378.3871300432672</v>
+        <v>378.3871300432685</v>
       </c>
       <c r="L21" t="n">
-        <v>680.7155789026183</v>
+        <v>680.7155789026195</v>
       </c>
       <c r="M21" t="n">
-        <v>802.9459706454775</v>
+        <v>802.9459706454787</v>
       </c>
       <c r="N21" t="n">
-        <v>973.3328842153099</v>
+        <v>973.3328842153112</v>
       </c>
       <c r="O21" t="n">
-        <v>1246.320652031104</v>
+        <v>1246.320652031106</v>
       </c>
       <c r="P21" t="n">
-        <v>1386.094105368536</v>
+        <v>1386.094105368537</v>
       </c>
       <c r="Q21" t="n">
-        <v>1386.094105368536</v>
+        <v>1386.094105368537</v>
       </c>
       <c r="R21" t="n">
-        <v>1023.467842742273</v>
+        <v>1250.411138787708</v>
       </c>
       <c r="S21" t="n">
-        <v>962.9757615887681</v>
+        <v>1189.919057634203</v>
       </c>
       <c r="T21" t="n">
-        <v>962.1910263776335</v>
+        <v>1189.134322423068</v>
       </c>
       <c r="U21" t="n">
-        <v>962.1910263776335</v>
+        <v>1189.134322423068</v>
       </c>
       <c r="V21" t="n">
-        <v>599.5647637513709</v>
+        <v>826.5080597967954</v>
       </c>
       <c r="W21" t="n">
-        <v>570.9050234384129</v>
+        <v>797.8483194838373</v>
       </c>
       <c r="X21" t="n">
-        <v>554.8820543016577</v>
+        <v>435.2220568575644</v>
       </c>
       <c r="Y21" t="n">
-        <v>391.3462626262626</v>
+        <v>435.2220568575644</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>793.4297405151412</v>
+        <v>567.2588171079217</v>
       </c>
       <c r="C22" t="n">
-        <v>923.391746333577</v>
+        <v>697.2208229263575</v>
       </c>
       <c r="D22" t="n">
-        <v>1040.670890458577</v>
+        <v>697.2208229263575</v>
       </c>
       <c r="E22" t="n">
-        <v>1162.45979466999</v>
+        <v>819.0097271377706</v>
       </c>
       <c r="F22" t="n">
-        <v>1162.45979466999</v>
+        <v>947.3306997297061</v>
       </c>
       <c r="G22" t="n">
-        <v>1162.45979466999</v>
+        <v>1104.816877092001</v>
       </c>
       <c r="H22" t="n">
-        <v>1336.999834583486</v>
+        <v>1279.356917005497</v>
       </c>
       <c r="I22" t="n">
-        <v>1407.578029630889</v>
+        <v>1279.356917005497</v>
       </c>
       <c r="J22" t="n">
-        <v>1407.578029630889</v>
+        <v>1279.356917005497</v>
       </c>
       <c r="K22" t="n">
-        <v>1407.578029630889</v>
+        <v>1407.57802963089</v>
       </c>
       <c r="L22" t="n">
-        <v>1405.976981152258</v>
+        <v>1405.976981152259</v>
       </c>
       <c r="M22" t="n">
-        <v>1307.297608813203</v>
+        <v>1307.297608813204</v>
       </c>
       <c r="N22" t="n">
-        <v>1157.099254920625</v>
+        <v>1157.099254920626</v>
       </c>
       <c r="O22" t="n">
-        <v>935.5151613816299</v>
+        <v>935.5151613816311</v>
       </c>
       <c r="P22" t="n">
-        <v>663.9643460641116</v>
+        <v>663.9643460641128</v>
       </c>
       <c r="Q22" t="n">
-        <v>349.0933698766388</v>
+        <v>349.0933698766401</v>
       </c>
       <c r="R22" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="S22" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="T22" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="U22" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="V22" t="n">
-        <v>231.501392885946</v>
+        <v>231.5013928859518</v>
       </c>
       <c r="W22" t="n">
-        <v>407.3523111456234</v>
+        <v>407.3523111456292</v>
       </c>
       <c r="X22" t="n">
-        <v>562.3431021698169</v>
+        <v>562.3431021698227</v>
       </c>
       <c r="Y22" t="n">
-        <v>677.7124028488491</v>
+        <v>567.2588171079217</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>81.95571988967217</v>
+        <v>82.32267908861158</v>
       </c>
       <c r="C23" t="n">
-        <v>36.0218024725066</v>
+        <v>36.38876167144601</v>
       </c>
       <c r="D23" t="n">
-        <v>29.61861485649671</v>
+        <v>29.98557405543612</v>
       </c>
       <c r="E23" t="n">
-        <v>29.61861485649671</v>
+        <v>29.6186148565789</v>
       </c>
       <c r="F23" t="n">
-        <v>28.71999999991908</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="G23" t="n">
-        <v>29.22685470210469</v>
+        <v>29.22685470218688</v>
       </c>
       <c r="H23" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="I23" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="J23" t="n">
-        <v>384.13</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="K23" t="n">
-        <v>739.54</v>
+        <v>384.130000000017</v>
       </c>
       <c r="L23" t="n">
-        <v>781.6198853266332</v>
+        <v>426.2098853266502</v>
       </c>
       <c r="M23" t="n">
-        <v>1137.029885326633</v>
+        <v>781.6198853266603</v>
       </c>
       <c r="N23" t="n">
-        <v>1137.029885326633</v>
+        <v>1137.02988532667</v>
       </c>
       <c r="O23" t="n">
-        <v>1137.029885326633</v>
+        <v>1137.02988532667</v>
       </c>
       <c r="P23" t="n">
-        <v>1175.090768901434</v>
+        <v>1175.090768901471</v>
       </c>
       <c r="Q23" t="n">
-        <v>1436</v>
+        <v>1436.000000000064</v>
       </c>
       <c r="R23" t="n">
-        <v>1436</v>
+        <v>1436.000000000064</v>
       </c>
       <c r="S23" t="n">
-        <v>1350.433909991055</v>
+        <v>1350.433909991119</v>
       </c>
       <c r="T23" t="n">
-        <v>1167.10409544365</v>
+        <v>1167.104095443714</v>
       </c>
       <c r="U23" t="n">
-        <v>924.2012544824197</v>
+        <v>924.5682136813591</v>
       </c>
       <c r="V23" t="n">
-        <v>696.0689068391632</v>
+        <v>696.4358660381026</v>
       </c>
       <c r="W23" t="n">
-        <v>459.3280220099233</v>
+        <v>459.6949812088627</v>
       </c>
       <c r="X23" t="n">
-        <v>269.1443518476327</v>
+        <v>269.5113110465721</v>
       </c>
       <c r="Y23" t="n">
-        <v>160.7429046932828</v>
+        <v>161.1098638922222</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>717.9203429896863</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="C24" t="n">
-        <v>717.9203429896863</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="D24" t="n">
-        <v>717.9203429896863</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="E24" t="n">
-        <v>371.7869114524009</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="F24" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="G24" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="H24" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="I24" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="J24" t="n">
-        <v>166.1559025337895</v>
+        <v>166.1559025337908</v>
       </c>
       <c r="K24" t="n">
-        <v>378.3871300432672</v>
+        <v>378.3871300432685</v>
       </c>
       <c r="L24" t="n">
-        <v>680.7155789026183</v>
+        <v>680.7155789026195</v>
       </c>
       <c r="M24" t="n">
-        <v>802.9459706454775</v>
+        <v>802.9459706454787</v>
       </c>
       <c r="N24" t="n">
-        <v>973.3328842153099</v>
+        <v>973.3328842153112</v>
       </c>
       <c r="O24" t="n">
-        <v>1246.320652031104</v>
+        <v>1246.320652031106</v>
       </c>
       <c r="P24" t="n">
-        <v>1386.094105368536</v>
+        <v>1386.094105368537</v>
       </c>
       <c r="Q24" t="n">
-        <v>1229.848306820881</v>
+        <v>1229.848306820882</v>
       </c>
       <c r="R24" t="n">
-        <v>867.2220441946188</v>
+        <v>1094.165340240053</v>
       </c>
       <c r="S24" t="n">
-        <v>774.0046231975242</v>
+        <v>1033.673259086549</v>
       </c>
       <c r="T24" t="n">
-        <v>773.2198879863896</v>
+        <v>1032.888523875414</v>
       </c>
       <c r="U24" t="n">
-        <v>773.2198879863896</v>
+        <v>670.2622612491409</v>
       </c>
       <c r="V24" t="n">
-        <v>762.6030524393996</v>
+        <v>307.6359986228679</v>
       </c>
       <c r="W24" t="n">
-        <v>733.9433121264415</v>
+        <v>44.74296913675637</v>
       </c>
       <c r="X24" t="n">
-        <v>717.9203429896863</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="Y24" t="n">
-        <v>717.9203429896863</v>
+        <v>28.72000000000127</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>706.521758200249</v>
+        <v>773.2393287252386</v>
       </c>
       <c r="C25" t="n">
-        <v>836.4837640186847</v>
+        <v>903.2013345436744</v>
       </c>
       <c r="D25" t="n">
-        <v>953.7629081436847</v>
+        <v>903.2013345436744</v>
       </c>
       <c r="E25" t="n">
-        <v>1075.551812355098</v>
+        <v>1024.990238755087</v>
       </c>
       <c r="F25" t="n">
-        <v>1075.551812355098</v>
+        <v>1153.311211347023</v>
       </c>
       <c r="G25" t="n">
-        <v>1233.037989717393</v>
+        <v>1310.797388709318</v>
       </c>
       <c r="H25" t="n">
-        <v>1407.578029630889</v>
+        <v>1407.57802963089</v>
       </c>
       <c r="I25" t="n">
-        <v>1407.578029630889</v>
+        <v>1407.57802963089</v>
       </c>
       <c r="J25" t="n">
-        <v>1407.578029630889</v>
+        <v>1407.57802963089</v>
       </c>
       <c r="K25" t="n">
-        <v>1407.578029630889</v>
+        <v>1407.57802963089</v>
       </c>
       <c r="L25" t="n">
-        <v>1405.976981152258</v>
+        <v>1405.976981152259</v>
       </c>
       <c r="M25" t="n">
-        <v>1307.297608813203</v>
+        <v>1307.297608813204</v>
       </c>
       <c r="N25" t="n">
-        <v>1157.099254920625</v>
+        <v>1157.099254920626</v>
       </c>
       <c r="O25" t="n">
-        <v>935.5151613816297</v>
+        <v>935.5151613816311</v>
       </c>
       <c r="P25" t="n">
-        <v>663.9643460641115</v>
+        <v>663.9643460641128</v>
       </c>
       <c r="Q25" t="n">
-        <v>349.0933698766388</v>
+        <v>349.0933698766401</v>
       </c>
       <c r="R25" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="S25" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="T25" t="n">
-        <v>28.72</v>
+        <v>28.72000000000127</v>
       </c>
       <c r="U25" t="n">
-        <v>117.6629359447851</v>
+        <v>279.237716900583</v>
       </c>
       <c r="V25" t="n">
-        <v>320.4443288307311</v>
+        <v>482.0191097865289</v>
       </c>
       <c r="W25" t="n">
-        <v>320.4443288307311</v>
+        <v>657.8700280462064</v>
       </c>
       <c r="X25" t="n">
-        <v>475.4351198549246</v>
+        <v>657.8700280462064</v>
       </c>
       <c r="Y25" t="n">
-        <v>590.8044205339569</v>
+        <v>773.2393287252386</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>373.2584740590099</v>
       </c>
       <c r="C26" t="n">
-        <v>28</v>
+        <v>278.8397081569959</v>
       </c>
       <c r="D26" t="n">
-        <v>28</v>
+        <v>223.9516720561375</v>
       </c>
       <c r="E26" t="n">
-        <v>28</v>
+        <v>175.0998643724318</v>
       </c>
       <c r="F26" t="n">
-        <v>28</v>
+        <v>125.7164010310057</v>
       </c>
       <c r="G26" t="n">
-        <v>28</v>
+        <v>77.7486984518664</v>
       </c>
       <c r="H26" t="n">
-        <v>28</v>
+        <v>28.00000000000128</v>
       </c>
       <c r="I26" t="n">
-        <v>28</v>
+        <v>28.00000000000128</v>
       </c>
       <c r="J26" t="n">
-        <v>28</v>
+        <v>374.5000000000181</v>
       </c>
       <c r="K26" t="n">
-        <v>374.5</v>
+        <v>664.9201146733969</v>
       </c>
       <c r="L26" t="n">
-        <v>707</v>
+        <v>707.00000000003</v>
       </c>
       <c r="M26" t="n">
-        <v>707</v>
+        <v>1053.500000000047</v>
       </c>
       <c r="N26" t="n">
-        <v>707</v>
+        <v>1053.500000000047</v>
       </c>
       <c r="O26" t="n">
-        <v>707</v>
+        <v>1053.500000000047</v>
       </c>
       <c r="P26" t="n">
-        <v>1053.5</v>
+        <v>1400.000000000064</v>
       </c>
       <c r="Q26" t="n">
-        <v>1400</v>
+        <v>1400.000000000064</v>
       </c>
       <c r="R26" t="n">
-        <v>1400</v>
+        <v>1400.000000000064</v>
       </c>
       <c r="S26" t="n">
-        <v>1400</v>
+        <v>1265.94906150627</v>
       </c>
       <c r="T26" t="n">
-        <v>1400</v>
+        <v>1265.94906150627</v>
       </c>
       <c r="U26" t="n">
-        <v>1103.83863756574</v>
+        <v>1265.94906150627</v>
       </c>
       <c r="V26" t="n">
-        <v>836.0525808888851</v>
+        <v>989.331865378165</v>
       </c>
       <c r="W26" t="n">
-        <v>550.8268475747966</v>
+        <v>896.0853216338065</v>
       </c>
       <c r="X26" t="n">
-        <v>312.1583289276575</v>
+        <v>657.4168029866674</v>
       </c>
       <c r="Y26" t="n">
-        <v>155.2720332884591</v>
+        <v>500.530507347469</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>33.15142671264575</v>
+        <v>33.15142671264703</v>
       </c>
       <c r="C27" t="n">
-        <v>28</v>
+        <v>28.00000000000128</v>
       </c>
       <c r="D27" t="n">
-        <v>28</v>
+        <v>28.00000000000128</v>
       </c>
       <c r="E27" t="n">
-        <v>28</v>
+        <v>28.00000000000128</v>
       </c>
       <c r="F27" t="n">
-        <v>28</v>
+        <v>28.00000000000128</v>
       </c>
       <c r="G27" t="n">
-        <v>28</v>
+        <v>28.00000000000128</v>
       </c>
       <c r="H27" t="n">
-        <v>28</v>
+        <v>28.00000000000128</v>
       </c>
       <c r="I27" t="n">
-        <v>28</v>
+        <v>28.00000000000128</v>
       </c>
       <c r="J27" t="n">
-        <v>165.4359025337895</v>
+        <v>165.4359025337908</v>
       </c>
       <c r="K27" t="n">
-        <v>377.6671300432672</v>
+        <v>377.6671300432685</v>
       </c>
       <c r="L27" t="n">
-        <v>679.9955789026183</v>
+        <v>679.9955789026196</v>
       </c>
       <c r="M27" t="n">
-        <v>802.2259706454774</v>
+        <v>802.2259706454788</v>
       </c>
       <c r="N27" t="n">
-        <v>972.6128842153099</v>
+        <v>972.6128842153113</v>
       </c>
       <c r="O27" t="n">
-        <v>1245.600652031104</v>
+        <v>1245.600652031106</v>
       </c>
       <c r="P27" t="n">
-        <v>1385.374105368536</v>
+        <v>1385.374105368537</v>
       </c>
       <c r="Q27" t="n">
-        <v>1385.374105368536</v>
+        <v>1229.128306820883</v>
       </c>
       <c r="R27" t="n">
-        <v>1031.838751833182</v>
+        <v>875.5929532855054</v>
       </c>
       <c r="S27" t="n">
-        <v>922.8618221948286</v>
+        <v>766.616023647152</v>
       </c>
       <c r="T27" t="n">
-        <v>660.1155670754713</v>
+        <v>717.3464399511689</v>
       </c>
       <c r="U27" t="n">
-        <v>306.5802135401177</v>
+        <v>363.8110864157982</v>
       </c>
       <c r="V27" t="n">
-        <v>247.4785295082791</v>
+        <v>304.7094023839596</v>
       </c>
       <c r="W27" t="n">
-        <v>170.3339407104725</v>
+        <v>227.564813586153</v>
       </c>
       <c r="X27" t="n">
-        <v>105.8261230888689</v>
+        <v>163.0569959645495</v>
       </c>
       <c r="Y27" t="n">
-        <v>61.99643342610698</v>
+        <v>119.2273063017875</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>556.413574304158</v>
+        <v>795.6634127634504</v>
       </c>
       <c r="C28" t="n">
-        <v>638.8555801225938</v>
+        <v>878.1054185818862</v>
       </c>
       <c r="D28" t="n">
-        <v>708.6147242475938</v>
+        <v>878.1054185818862</v>
       </c>
       <c r="E28" t="n">
-        <v>782.8836284590068</v>
+        <v>878.1054185818862</v>
       </c>
       <c r="F28" t="n">
-        <v>782.8836284590068</v>
+        <v>901.1427478841081</v>
       </c>
       <c r="G28" t="n">
-        <v>892.8498058213019</v>
+        <v>1011.108925246403</v>
       </c>
       <c r="H28" t="n">
-        <v>892.8498058213019</v>
+        <v>1138.128965159899</v>
       </c>
       <c r="I28" t="n">
-        <v>1074.019728036073</v>
+        <v>1319.298887374671</v>
       </c>
       <c r="J28" t="n">
-        <v>1400</v>
+        <v>1319.298887374671</v>
       </c>
       <c r="K28" t="n">
-        <v>1400</v>
+        <v>1400.000000000064</v>
       </c>
       <c r="L28" t="n">
-        <v>1400</v>
+        <v>1400.000000000064</v>
       </c>
       <c r="M28" t="n">
-        <v>1400</v>
+        <v>1400.000000000064</v>
       </c>
       <c r="N28" t="n">
-        <v>1329.486345549247</v>
+        <v>1201.316797622637</v>
       </c>
       <c r="O28" t="n">
-        <v>1059.417403525403</v>
+        <v>931.2478555987936</v>
       </c>
       <c r="P28" t="n">
-        <v>739.3817397230366</v>
+        <v>611.212191796427</v>
       </c>
       <c r="Q28" t="n">
-        <v>385.8463861876831</v>
+        <v>381.535353535372</v>
       </c>
       <c r="R28" t="n">
-        <v>32.31103265232954</v>
+        <v>28.00000000000128</v>
       </c>
       <c r="S28" t="n">
-        <v>28</v>
+        <v>28.00000000000128</v>
       </c>
       <c r="T28" t="n">
-        <v>28</v>
+        <v>173.0267463719209</v>
       </c>
       <c r="U28" t="n">
-        <v>136.7746248132102</v>
+        <v>376.0244632725026</v>
       </c>
       <c r="V28" t="n">
-        <v>292.0360176991562</v>
+        <v>531.2858561584486</v>
       </c>
       <c r="W28" t="n">
-        <v>420.3669359588337</v>
+        <v>659.6167744181261</v>
       </c>
       <c r="X28" t="n">
-        <v>420.3669359588337</v>
+        <v>659.6167744181261</v>
       </c>
       <c r="Y28" t="n">
-        <v>488.2162366378659</v>
+        <v>727.4660750971583</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>71.68809239125909</v>
+        <v>157.8021512951801</v>
       </c>
       <c r="C29" t="n">
-        <v>71.68809239125909</v>
+        <v>157.8021512951801</v>
       </c>
       <c r="D29" t="n">
-        <v>71.68809239125909</v>
+        <v>157.8021512951801</v>
       </c>
       <c r="E29" t="n">
-        <v>71.68809239125909</v>
+        <v>115.0109496720804</v>
       </c>
       <c r="F29" t="n">
-        <v>71.68809239125909</v>
+        <v>71.68809239126037</v>
       </c>
       <c r="G29" t="n">
-        <v>71.68809239125909</v>
+        <v>71.68809239126037</v>
       </c>
       <c r="H29" t="n">
-        <v>28</v>
+        <v>28.00000000000128</v>
       </c>
       <c r="I29" t="n">
-        <v>28</v>
+        <v>28.00000000000128</v>
       </c>
       <c r="J29" t="n">
-        <v>28</v>
+        <v>28.00000000000128</v>
       </c>
       <c r="K29" t="n">
-        <v>374.5</v>
+        <v>374.5000000000171</v>
       </c>
       <c r="L29" t="n">
-        <v>707</v>
+        <v>416.5798853266502</v>
       </c>
       <c r="M29" t="n">
-        <v>707</v>
+        <v>763.0798853266652</v>
       </c>
       <c r="N29" t="n">
-        <v>707</v>
+        <v>1015.439116425248</v>
       </c>
       <c r="O29" t="n">
-        <v>707</v>
+        <v>1015.439116425248</v>
       </c>
       <c r="P29" t="n">
-        <v>1053.5</v>
+        <v>1053.500000000049</v>
       </c>
       <c r="Q29" t="n">
-        <v>1400</v>
+        <v>1400.000000000064</v>
       </c>
       <c r="R29" t="n">
-        <v>1400</v>
+        <v>1400.000000000064</v>
       </c>
       <c r="S29" t="n">
-        <v>1400</v>
+        <v>1272.009667566876</v>
       </c>
       <c r="T29" t="n">
-        <v>1294.94416825102</v>
+        <v>1090.957470781287</v>
       </c>
       <c r="U29" t="n">
-        <v>1004.843411877366</v>
+        <v>1090.957470781287</v>
       </c>
       <c r="V29" t="n">
-        <v>734.2868218098669</v>
+        <v>820.4008807137878</v>
       </c>
       <c r="W29" t="n">
-        <v>455.1216945563845</v>
+        <v>541.2357534603054</v>
       </c>
       <c r="X29" t="n">
-        <v>222.5137819698514</v>
+        <v>308.6278408737724</v>
       </c>
       <c r="Y29" t="n">
-        <v>71.68809239125909</v>
+        <v>157.8021512951801</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>43.05554214903191</v>
+        <v>593.7598791274972</v>
       </c>
       <c r="C30" t="n">
-        <v>28</v>
+        <v>593.7598791274972</v>
       </c>
       <c r="D30" t="n">
-        <v>28</v>
+        <v>242.3076701399188</v>
       </c>
       <c r="E30" t="n">
-        <v>28</v>
+        <v>242.3076701399188</v>
       </c>
       <c r="F30" t="n">
-        <v>28</v>
+        <v>242.3076701399188</v>
       </c>
       <c r="G30" t="n">
-        <v>28</v>
+        <v>242.3076701399188</v>
       </c>
       <c r="H30" t="n">
-        <v>28</v>
+        <v>242.3076701399188</v>
       </c>
       <c r="I30" t="n">
-        <v>28</v>
+        <v>28.00000000000128</v>
       </c>
       <c r="J30" t="n">
-        <v>165.4359025337895</v>
+        <v>165.4359025337908</v>
       </c>
       <c r="K30" t="n">
-        <v>377.6671300432672</v>
+        <v>377.6671300432685</v>
       </c>
       <c r="L30" t="n">
-        <v>679.9955789026183</v>
+        <v>679.9955789026196</v>
       </c>
       <c r="M30" t="n">
-        <v>802.2259706454774</v>
+        <v>802.2259706454788</v>
       </c>
       <c r="N30" t="n">
-        <v>972.6128842153099</v>
+        <v>972.6128842153113</v>
       </c>
       <c r="O30" t="n">
-        <v>1245.600652031104</v>
+        <v>1245.600652031106</v>
       </c>
       <c r="P30" t="n">
-        <v>1385.374105368536</v>
+        <v>1385.374105368537</v>
       </c>
       <c r="Q30" t="n">
-        <v>1385.374105368536</v>
+        <v>1229.128306820883</v>
       </c>
       <c r="R30" t="n">
-        <v>1031.838751833182</v>
+        <v>1051.021097815811</v>
       </c>
       <c r="S30" t="n">
-        <v>678.3033982978284</v>
+        <v>948.1047742380639</v>
       </c>
       <c r="T30" t="n">
-        <v>324.7680447624748</v>
+        <v>904.8957966026869</v>
       </c>
       <c r="U30" t="n">
-        <v>286.1812986734735</v>
+        <v>866.3090505136856</v>
       </c>
       <c r="V30" t="n">
-        <v>233.140220702241</v>
+        <v>813.2679725424532</v>
       </c>
       <c r="W30" t="n">
-        <v>162.0562379650405</v>
+        <v>742.1839898052526</v>
       </c>
       <c r="X30" t="n">
-        <v>103.609026404043</v>
+        <v>683.7367782442551</v>
       </c>
       <c r="Y30" t="n">
-        <v>65.83994280188708</v>
+        <v>645.9676946420992</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>810.4432855279651</v>
+        <v>389.5544275837683</v>
       </c>
       <c r="C31" t="n">
-        <v>898.8252913464009</v>
+        <v>389.5544275837683</v>
       </c>
       <c r="D31" t="n">
-        <v>974.524435471401</v>
+        <v>465.2535717087684</v>
       </c>
       <c r="E31" t="n">
-        <v>1054.733339682814</v>
+        <v>545.4624759201814</v>
       </c>
       <c r="F31" t="n">
-        <v>1141.47431227475</v>
+        <v>545.4624759201814</v>
       </c>
       <c r="G31" t="n">
-        <v>1257.380489637045</v>
+        <v>661.3686532824765</v>
       </c>
       <c r="H31" t="n">
-        <v>1390.34052955054</v>
+        <v>794.3286931959725</v>
       </c>
       <c r="I31" t="n">
-        <v>1400</v>
+        <v>981.438615410744</v>
       </c>
       <c r="J31" t="n">
-        <v>1400</v>
+        <v>1313.358887374671</v>
       </c>
       <c r="K31" t="n">
-        <v>1400</v>
+        <v>1400.000000000064</v>
       </c>
       <c r="L31" t="n">
-        <v>1355.974709097127</v>
+        <v>1400.000000000064</v>
       </c>
       <c r="M31" t="n">
-        <v>1355.974709097127</v>
+        <v>1400.000000000064</v>
       </c>
       <c r="N31" t="n">
-        <v>1163.352112780306</v>
+        <v>1207.377403683243</v>
       </c>
       <c r="O31" t="n">
-        <v>899.3437768170687</v>
+        <v>943.3690677200058</v>
       </c>
       <c r="P31" t="n">
-        <v>585.368719075308</v>
+        <v>629.3940099782451</v>
       </c>
       <c r="Q31" t="n">
-        <v>381.5353535353536</v>
+        <v>381.5353535353701</v>
       </c>
       <c r="R31" t="n">
-        <v>28</v>
+        <v>28.00000000000128</v>
       </c>
       <c r="S31" t="n">
-        <v>28</v>
+        <v>29.71475689745308</v>
       </c>
       <c r="T31" t="n">
-        <v>178.9667463719196</v>
+        <v>180.6815032693727</v>
       </c>
       <c r="U31" t="n">
-        <v>387.9044632725013</v>
+        <v>180.6815032693727</v>
       </c>
       <c r="V31" t="n">
-        <v>549.1058561584473</v>
+        <v>180.6815032693727</v>
       </c>
       <c r="W31" t="n">
-        <v>549.1058561584473</v>
+        <v>276.1436365595748</v>
       </c>
       <c r="X31" t="n">
-        <v>662.5166471826408</v>
+        <v>389.5544275837683</v>
       </c>
       <c r="Y31" t="n">
-        <v>736.3059478616731</v>
+        <v>389.5544275837683</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>67.39331135655951</v>
+        <v>67.73589291196461</v>
       </c>
       <c r="C32" t="n">
-        <v>27.52</v>
+        <v>27.8625815554051</v>
       </c>
       <c r="D32" t="n">
-        <v>27.52</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="E32" t="n">
-        <v>27.52</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="F32" t="n">
-        <v>27.52</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="G32" t="n">
-        <v>27.52</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="H32" t="n">
-        <v>27.52</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="I32" t="n">
-        <v>27.52</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="J32" t="n">
-        <v>27.52</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="K32" t="n">
-        <v>61.43929542713568</v>
+        <v>312.2401146734236</v>
       </c>
       <c r="L32" t="n">
-        <v>103.5191807537689</v>
+        <v>354.3200000000568</v>
       </c>
       <c r="M32" t="n">
-        <v>444.0791807537689</v>
+        <v>694.8800000000695</v>
       </c>
       <c r="N32" t="n">
-        <v>784.6391807537689</v>
+        <v>694.8800000000695</v>
       </c>
       <c r="O32" t="n">
-        <v>784.6391807537689</v>
+        <v>694.8800000000695</v>
       </c>
       <c r="P32" t="n">
-        <v>1125.199180753769</v>
+        <v>1035.440000000082</v>
       </c>
       <c r="Q32" t="n">
-        <v>1376</v>
+        <v>1376.000000000095</v>
       </c>
       <c r="R32" t="n">
-        <v>1376</v>
+        <v>1376.000000000064</v>
       </c>
       <c r="S32" t="n">
-        <v>1296.494516051661</v>
+        <v>1296.494516051725</v>
       </c>
       <c r="T32" t="n">
-        <v>1119.225307564862</v>
+        <v>1119.225307564926</v>
       </c>
       <c r="U32" t="n">
-        <v>877.609399676057</v>
+        <v>877.6093996761207</v>
       </c>
       <c r="V32" t="n">
-        <v>655.5376580934067</v>
+        <v>655.5376580934703</v>
       </c>
       <c r="W32" t="n">
-        <v>424.8573793247728</v>
+        <v>426.9263768503976</v>
       </c>
       <c r="X32" t="n">
-        <v>240.7343152230882</v>
+        <v>242.803312748713</v>
       </c>
       <c r="Y32" t="n">
-        <v>140.1198900995641</v>
+        <v>140.4624716549692</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27.52</v>
+        <v>998.5826390244337</v>
       </c>
       <c r="C33" t="n">
-        <v>27.52</v>
+        <v>721.1281790120472</v>
       </c>
       <c r="D33" t="n">
-        <v>27.52</v>
+        <v>373.6534315372868</v>
       </c>
       <c r="E33" t="n">
-        <v>27.52</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="F33" t="n">
-        <v>27.52</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="G33" t="n">
-        <v>27.52</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="H33" t="n">
-        <v>27.52</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="I33" t="n">
-        <v>27.52</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="J33" t="n">
-        <v>164.9559025337895</v>
+        <v>164.9559025337908</v>
       </c>
       <c r="K33" t="n">
-        <v>377.1871300432672</v>
+        <v>377.1871300432685</v>
       </c>
       <c r="L33" t="n">
-        <v>679.5155789026182</v>
+        <v>679.5155789026196</v>
       </c>
       <c r="M33" t="n">
-        <v>801.7459706454774</v>
+        <v>801.7459706454788</v>
       </c>
       <c r="N33" t="n">
-        <v>972.1328842153099</v>
+        <v>972.1328842153113</v>
       </c>
       <c r="O33" t="n">
-        <v>1236.226546662569</v>
+        <v>1236.226546662664</v>
       </c>
       <c r="P33" t="n">
-        <v>1376</v>
+        <v>1376.000000000095</v>
       </c>
       <c r="Q33" t="n">
-        <v>1376</v>
+        <v>1219.754201452441</v>
       </c>
       <c r="R33" t="n">
-        <v>1138.894310079674</v>
+        <v>1090.131840932218</v>
       </c>
       <c r="S33" t="n">
-        <v>1084.462834986776</v>
+        <v>1035.700365839319</v>
       </c>
       <c r="T33" t="n">
-        <v>736.9880875120281</v>
+        <v>1035.700365839319</v>
       </c>
       <c r="U33" t="n">
-        <v>736.9880875120281</v>
+        <v>1035.700365839319</v>
       </c>
       <c r="V33" t="n">
-        <v>732.431858025644</v>
+        <v>1031.144136352935</v>
       </c>
       <c r="W33" t="n">
-        <v>384.9571105508965</v>
+        <v>1008.545002100583</v>
       </c>
       <c r="X33" t="n">
-        <v>374.9947474747475</v>
+        <v>998.5826390244337</v>
       </c>
       <c r="Y33" t="n">
-        <v>374.9947474747475</v>
+        <v>998.5826390244337</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>956.7301197494307</v>
+        <v>268.7661785512762</v>
       </c>
       <c r="C34" t="n">
-        <v>956.7301197494307</v>
+        <v>404.668184369712</v>
       </c>
       <c r="D34" t="n">
-        <v>956.7301197494307</v>
+        <v>527.8873284947121</v>
       </c>
       <c r="E34" t="n">
-        <v>956.7301197494307</v>
+        <v>655.6162327061251</v>
       </c>
       <c r="F34" t="n">
-        <v>956.7301197494307</v>
+        <v>789.8772052980605</v>
       </c>
       <c r="G34" t="n">
-        <v>995.2514975623634</v>
+        <v>953.3033826603556</v>
       </c>
       <c r="H34" t="n">
-        <v>995.2514975623634</v>
+        <v>1133.783422573852</v>
       </c>
       <c r="I34" t="n">
-        <v>1229.881419777135</v>
+        <v>1368.413344788623</v>
       </c>
       <c r="J34" t="n">
-        <v>1229.881419777135</v>
+        <v>1368.413344788623</v>
       </c>
       <c r="K34" t="n">
-        <v>1364.042532402528</v>
+        <v>1368.413344788623</v>
       </c>
       <c r="L34" t="n">
-        <v>1368.413344788622</v>
+        <v>1368.413344788623</v>
       </c>
       <c r="M34" t="n">
-        <v>1275.794578510172</v>
+        <v>1275.794578510174</v>
       </c>
       <c r="N34" t="n">
-        <v>1131.656830678201</v>
+        <v>1131.656830678202</v>
       </c>
       <c r="O34" t="n">
-        <v>916.1333431998115</v>
+        <v>916.1333431998129</v>
       </c>
       <c r="P34" t="n">
-        <v>650.6431339428993</v>
+        <v>650.6431339429007</v>
       </c>
       <c r="Q34" t="n">
-        <v>341.8327638160327</v>
+        <v>341.832763816034</v>
       </c>
       <c r="R34" t="n">
-        <v>27.52</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="S34" t="n">
-        <v>27.52</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="T34" t="n">
-        <v>27.52</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="U34" t="n">
-        <v>283.9777169005817</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="V34" t="n">
-        <v>492.6991097865276</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="W34" t="n">
-        <v>674.490028046205</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="X34" t="n">
-        <v>835.4208190703985</v>
+        <v>27.52000000000127</v>
       </c>
       <c r="Y34" t="n">
-        <v>956.7301197494307</v>
+        <v>147.1088408849841</v>
       </c>
     </row>
     <row r="35">
@@ -6931,22 +6931,22 @@
         <v>360.59</v>
       </c>
       <c r="K35" t="n">
-        <v>694.2199999999999</v>
+        <v>394.5092954271356</v>
       </c>
       <c r="L35" t="n">
-        <v>976.3091164251992</v>
+        <v>436.5891807537688</v>
       </c>
       <c r="M35" t="n">
-        <v>1309.939116425199</v>
+        <v>436.5891807537689</v>
       </c>
       <c r="N35" t="n">
-        <v>1309.939116425199</v>
+        <v>436.5891807537689</v>
       </c>
       <c r="O35" t="n">
-        <v>1309.939116425199</v>
+        <v>770.2191807537688</v>
       </c>
       <c r="P35" t="n">
-        <v>1348</v>
+        <v>1014.37</v>
       </c>
       <c r="Q35" t="n">
         <v>1348</v>
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>915.7891418548083</v>
+        <v>26.96</v>
       </c>
       <c r="C36" t="n">
-        <v>915.7891418548083</v>
+        <v>26.96</v>
       </c>
       <c r="D36" t="n">
-        <v>915.7891418548083</v>
+        <v>26.96</v>
       </c>
       <c r="E36" t="n">
-        <v>915.7891418548083</v>
+        <v>26.96</v>
       </c>
       <c r="F36" t="n">
-        <v>575.3851014507679</v>
+        <v>26.96</v>
       </c>
       <c r="G36" t="n">
-        <v>575.3851014507679</v>
+        <v>26.96</v>
       </c>
       <c r="H36" t="n">
-        <v>241.2676701399176</v>
+        <v>26.96</v>
       </c>
       <c r="I36" t="n">
         <v>26.96</v>
@@ -7019,7 +7019,7 @@
         <v>801.1859706454775</v>
       </c>
       <c r="N36" t="n">
-        <v>971.57288421531</v>
+        <v>935.2387788467745</v>
       </c>
       <c r="O36" t="n">
         <v>1208.226546662569</v>
@@ -7028,31 +7028,31 @@
         <v>1348</v>
       </c>
       <c r="Q36" t="n">
-        <v>1348</v>
+        <v>1227.691277220718</v>
       </c>
       <c r="R36" t="n">
-        <v>1007.59595959596</v>
+        <v>1101.099219730798</v>
       </c>
       <c r="S36" t="n">
-        <v>956.1947875333639</v>
+        <v>1049.698047668202</v>
       </c>
       <c r="T36" t="n">
-        <v>956.1947875333639</v>
+        <v>1049.698047668202</v>
       </c>
       <c r="U36" t="n">
-        <v>943.8159595787843</v>
+        <v>1049.698047668202</v>
       </c>
       <c r="V36" t="n">
-        <v>942.2900331227033</v>
+        <v>1048.172121212121</v>
       </c>
       <c r="W36" t="n">
-        <v>922.7212019006544</v>
+        <v>707.7680808080809</v>
       </c>
       <c r="X36" t="n">
-        <v>915.7891418548083</v>
+        <v>367.3640404040404</v>
       </c>
       <c r="Y36" t="n">
-        <v>915.7891418548083</v>
+        <v>26.96</v>
       </c>
     </row>
     <row r="37">
@@ -7062,46 +7062,46 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>852.9155686273834</v>
+        <v>815.0089732532157</v>
       </c>
       <c r="C37" t="n">
-        <v>991.7875744458192</v>
+        <v>953.8809790716515</v>
       </c>
       <c r="D37" t="n">
-        <v>1117.976718570819</v>
+        <v>1080.070123196652</v>
       </c>
       <c r="E37" t="n">
-        <v>1248.675622782232</v>
+        <v>1210.769027408065</v>
       </c>
       <c r="F37" t="n">
-        <v>1248.675622782232</v>
+        <v>1348</v>
       </c>
       <c r="G37" t="n">
-        <v>1248.675622782232</v>
+        <v>1348</v>
       </c>
       <c r="H37" t="n">
-        <v>1248.675622782232</v>
+        <v>1348</v>
       </c>
       <c r="I37" t="n">
-        <v>1248.675622782232</v>
+        <v>1348</v>
       </c>
       <c r="J37" t="n">
-        <v>1248.675622782232</v>
+        <v>1348</v>
       </c>
       <c r="K37" t="n">
-        <v>1340.659187613906</v>
+        <v>1348</v>
       </c>
       <c r="L37" t="n">
         <v>1348</v>
       </c>
       <c r="M37" t="n">
-        <v>1260.083063358657</v>
+        <v>1258.411536751854</v>
       </c>
       <c r="N37" t="n">
-        <v>1118.975618556988</v>
+        <v>1117.304091950185</v>
       </c>
       <c r="O37" t="n">
-        <v>906.4824341089025</v>
+        <v>904.810907502099</v>
       </c>
       <c r="P37" t="n">
         <v>644.0225278822933</v>
@@ -7122,16 +7122,16 @@
         <v>228.4167463719196</v>
       </c>
       <c r="V37" t="n">
-        <v>440.1081392578656</v>
+        <v>228.4167463719196</v>
       </c>
       <c r="W37" t="n">
-        <v>440.1081392578656</v>
+        <v>402.2015438836978</v>
       </c>
       <c r="X37" t="n">
-        <v>604.0089302820591</v>
+        <v>566.1023349078913</v>
       </c>
       <c r="Y37" t="n">
-        <v>728.2882309610914</v>
+        <v>690.3816355869236</v>
       </c>
     </row>
     <row r="38">
@@ -7165,22 +7165,22 @@
         <v>26.96</v>
       </c>
       <c r="J38" t="n">
-        <v>271.1108192462312</v>
+        <v>360.59</v>
       </c>
       <c r="K38" t="n">
-        <v>305.0301146733668</v>
+        <v>394.5092954271356</v>
       </c>
       <c r="L38" t="n">
-        <v>347.11</v>
+        <v>436.5891807537688</v>
       </c>
       <c r="M38" t="n">
-        <v>347.11</v>
+        <v>770.2191807537688</v>
       </c>
       <c r="N38" t="n">
-        <v>347.11</v>
+        <v>976.3091164251992</v>
       </c>
       <c r="O38" t="n">
-        <v>680.74</v>
+        <v>976.3091164251992</v>
       </c>
       <c r="P38" t="n">
         <v>1014.37</v>
@@ -7192,7 +7192,7 @@
         <v>1348</v>
       </c>
       <c r="S38" t="n">
-        <v>1273.418507779457</v>
+        <v>1273.418507779456</v>
       </c>
       <c r="T38" t="n">
         <v>1099.179602322961</v>
@@ -7220,37 +7220,37 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>581.6717105439579</v>
+        <v>26.96</v>
       </c>
       <c r="C39" t="n">
-        <v>581.6717105439579</v>
+        <v>26.96</v>
       </c>
       <c r="D39" t="n">
-        <v>581.6717105439579</v>
+        <v>26.96</v>
       </c>
       <c r="E39" t="n">
-        <v>241.2676701399176</v>
+        <v>26.96</v>
       </c>
       <c r="F39" t="n">
-        <v>241.2676701399176</v>
+        <v>26.96</v>
       </c>
       <c r="G39" t="n">
-        <v>241.2676701399176</v>
+        <v>26.96</v>
       </c>
       <c r="H39" t="n">
-        <v>241.2676701399176</v>
+        <v>26.96</v>
       </c>
       <c r="I39" t="n">
         <v>26.96</v>
       </c>
       <c r="J39" t="n">
-        <v>164.3959025337895</v>
+        <v>128.0617971652541</v>
       </c>
       <c r="K39" t="n">
-        <v>376.6271300432672</v>
+        <v>340.2930246747318</v>
       </c>
       <c r="L39" t="n">
-        <v>678.9555789026183</v>
+        <v>642.6214735340828</v>
       </c>
       <c r="M39" t="n">
         <v>764.851865276942</v>
@@ -7265,31 +7265,31 @@
         <v>1348</v>
       </c>
       <c r="Q39" t="n">
-        <v>1348</v>
+        <v>1191.754201452346</v>
       </c>
       <c r="R39" t="n">
-        <v>1221.40794251008</v>
+        <v>1065.162143962426</v>
       </c>
       <c r="S39" t="n">
-        <v>950.1025686719743</v>
+        <v>1013.76097189983</v>
       </c>
       <c r="T39" t="n">
-        <v>609.6985282679339</v>
+        <v>1013.76097189983</v>
       </c>
       <c r="U39" t="n">
-        <v>609.6985282679339</v>
+        <v>1013.76097189983</v>
       </c>
       <c r="V39" t="n">
-        <v>608.1726018118529</v>
+        <v>673.3569314957896</v>
       </c>
       <c r="W39" t="n">
-        <v>588.603770589804</v>
+        <v>332.9528910917492</v>
       </c>
       <c r="X39" t="n">
-        <v>581.6717105439579</v>
+        <v>26.96</v>
       </c>
       <c r="Y39" t="n">
-        <v>581.6717105439579</v>
+        <v>26.96</v>
       </c>
     </row>
     <row r="40">
@@ -7299,25 +7299,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1060.780831994609</v>
+        <v>328.0713952427762</v>
       </c>
       <c r="C40" t="n">
-        <v>1060.780831994609</v>
+        <v>359.0940271949954</v>
       </c>
       <c r="D40" t="n">
-        <v>1186.969976119609</v>
+        <v>485.2831713199955</v>
       </c>
       <c r="E40" t="n">
-        <v>1317.668880331022</v>
+        <v>615.9820755314086</v>
       </c>
       <c r="F40" t="n">
-        <v>1340.659187613906</v>
+        <v>753.213048123344</v>
       </c>
       <c r="G40" t="n">
-        <v>1340.659187613906</v>
+        <v>919.6092254856392</v>
       </c>
       <c r="H40" t="n">
-        <v>1340.659187613906</v>
+        <v>1103.059265399135</v>
       </c>
       <c r="I40" t="n">
         <v>1340.659187613906</v>
@@ -7332,43 +7332,43 @@
         <v>1348</v>
       </c>
       <c r="M40" t="n">
-        <v>1260.083063358657</v>
+        <v>1258.411536751854</v>
       </c>
       <c r="N40" t="n">
-        <v>1118.975618556988</v>
+        <v>1117.304091950185</v>
       </c>
       <c r="O40" t="n">
-        <v>906.4824341089025</v>
+        <v>904.810907502099</v>
       </c>
       <c r="P40" t="n">
-        <v>644.0225278822934</v>
+        <v>642.3510012754898</v>
       </c>
       <c r="Q40" t="n">
-        <v>338.2424607857296</v>
+        <v>336.5709341789262</v>
       </c>
       <c r="R40" t="n">
         <v>26.96</v>
       </c>
       <c r="S40" t="n">
-        <v>79.16475689745182</v>
+        <v>79.16475689745181</v>
       </c>
       <c r="T40" t="n">
-        <v>280.6215032693714</v>
+        <v>79.16475689745181</v>
       </c>
       <c r="U40" t="n">
-        <v>540.0492201699531</v>
+        <v>79.16475689745181</v>
       </c>
       <c r="V40" t="n">
-        <v>751.7406130558991</v>
+        <v>79.16475689745181</v>
       </c>
       <c r="W40" t="n">
-        <v>936.5015313155765</v>
+        <v>79.16475689745181</v>
       </c>
       <c r="X40" t="n">
-        <v>936.5015313155765</v>
+        <v>79.16475689745181</v>
       </c>
       <c r="Y40" t="n">
-        <v>1060.780831994609</v>
+        <v>203.4440575764841</v>
       </c>
     </row>
     <row r="41">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26.96</v>
+        <v>479.4235783094229</v>
       </c>
       <c r="C41" t="n">
-        <v>26.96</v>
+        <v>341.5704689730654</v>
       </c>
       <c r="D41" t="n">
-        <v>26.96</v>
+        <v>243.2480894378636</v>
       </c>
       <c r="E41" t="n">
-        <v>26.96</v>
+        <v>212.9608486619782</v>
       </c>
       <c r="F41" t="n">
-        <v>26.96</v>
+        <v>120.1430418862086</v>
       </c>
       <c r="G41" t="n">
-        <v>26.96</v>
+        <v>120.1430418862086</v>
       </c>
       <c r="H41" t="n">
         <v>26.96</v>
@@ -7402,25 +7402,25 @@
         <v>26.96</v>
       </c>
       <c r="J41" t="n">
-        <v>360.59</v>
+        <v>275.1298209980636</v>
       </c>
       <c r="K41" t="n">
-        <v>394.5092954271356</v>
+        <v>309.0491164251993</v>
       </c>
       <c r="L41" t="n">
-        <v>436.5891807537688</v>
+        <v>642.6791164251993</v>
       </c>
       <c r="M41" t="n">
-        <v>436.5891807537689</v>
+        <v>976.3091164251992</v>
       </c>
       <c r="N41" t="n">
-        <v>436.5891807537689</v>
+        <v>1309.939116425199</v>
       </c>
       <c r="O41" t="n">
-        <v>770.2191807537688</v>
+        <v>1309.939116425199</v>
       </c>
       <c r="P41" t="n">
-        <v>1103.849180753769</v>
+        <v>1348</v>
       </c>
       <c r="Q41" t="n">
         <v>1348</v>
@@ -7429,25 +7429,25 @@
         <v>1348</v>
       </c>
       <c r="S41" t="n">
-        <v>1170.514718071863</v>
+        <v>1348</v>
       </c>
       <c r="T41" t="n">
-        <v>968.7101075125343</v>
+        <v>1348</v>
       </c>
       <c r="U41" t="n">
-        <v>629.1144016439309</v>
+        <v>1008.404294131397</v>
       </c>
       <c r="V41" t="n">
-        <v>309.0628620814825</v>
+        <v>1008.404294131397</v>
       </c>
       <c r="W41" t="n">
-        <v>309.0628620814825</v>
+        <v>679.7442173829647</v>
       </c>
       <c r="X41" t="n">
-        <v>26.96</v>
+        <v>679.7442173829647</v>
       </c>
       <c r="Y41" t="n">
-        <v>26.96</v>
+        <v>479.4235783094229</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>198.3919379477106</v>
+        <v>296.6004417138158</v>
       </c>
       <c r="C42" t="n">
-        <v>149.8061678007214</v>
+        <v>248.0146715668266</v>
       </c>
       <c r="D42" t="n">
-        <v>114.5155749747592</v>
+        <v>212.7240787408643</v>
       </c>
       <c r="E42" t="n">
-        <v>84.54375959908984</v>
+        <v>182.752263365195</v>
       </c>
       <c r="F42" t="n">
-        <v>57.63846430830512</v>
+        <v>155.8469680744103</v>
       </c>
       <c r="G42" t="n">
-        <v>44.91581514923423</v>
+        <v>143.1243189153394</v>
       </c>
       <c r="H42" t="n">
-        <v>26.96</v>
+        <v>125.1685037661052</v>
       </c>
       <c r="I42" t="n">
         <v>26.96</v>
@@ -7487,7 +7487,7 @@
         <v>376.6271300432672</v>
       </c>
       <c r="L42" t="n">
-        <v>642.6214735340828</v>
+        <v>678.9555789026183</v>
       </c>
       <c r="M42" t="n">
         <v>764.851865276942</v>
@@ -7505,28 +7505,28 @@
         <v>1348</v>
       </c>
       <c r="R42" t="n">
-        <v>1022.189337733874</v>
+        <v>1120.397841499979</v>
       </c>
       <c r="S42" t="n">
-        <v>869.778064661177</v>
+        <v>967.9865684272822</v>
       </c>
       <c r="T42" t="n">
-        <v>777.0741375308505</v>
+        <v>875.2826412969557</v>
       </c>
       <c r="U42" t="n">
-        <v>688.9924419468997</v>
+        <v>787.2009457130049</v>
       </c>
       <c r="V42" t="n">
-        <v>586.4564144807177</v>
+        <v>684.6649182468229</v>
       </c>
       <c r="W42" t="n">
-        <v>465.8774822485677</v>
+        <v>564.0859860146729</v>
       </c>
       <c r="X42" t="n">
-        <v>357.9353211926207</v>
+        <v>456.1438249587259</v>
       </c>
       <c r="Y42" t="n">
-        <v>270.6712880955153</v>
+        <v>368.8797918616204</v>
       </c>
     </row>
     <row r="43">
@@ -7554,10 +7554,10 @@
         <v>808.4914078967222</v>
       </c>
       <c r="H43" t="n">
-        <v>887.8586931959089</v>
+        <v>892.9414478102182</v>
       </c>
       <c r="I43" t="n">
-        <v>1026.45861541068</v>
+        <v>1031.54137002499</v>
       </c>
       <c r="J43" t="n">
         <v>1309.868887374607</v>
@@ -7575,16 +7575,16 @@
         <v>1348</v>
       </c>
       <c r="O43" t="n">
-        <v>1095.917497298794</v>
+        <v>1034.496714541813</v>
       </c>
       <c r="P43" t="n">
-        <v>755.5134568947537</v>
+        <v>694.0926741377725</v>
       </c>
       <c r="Q43" t="n">
-        <v>415.1094164907134</v>
+        <v>367.3640404040404</v>
       </c>
       <c r="R43" t="n">
-        <v>74.70537608667298</v>
+        <v>26.96</v>
       </c>
       <c r="S43" t="n">
         <v>26.96</v>
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26.96</v>
+        <v>131.3429855958079</v>
       </c>
       <c r="C44" t="n">
-        <v>26.96</v>
+        <v>131.3429855958079</v>
       </c>
       <c r="D44" t="n">
         <v>26.96</v>
@@ -7642,13 +7642,13 @@
         <v>26.96</v>
       </c>
       <c r="K44" t="n">
-        <v>360.59</v>
+        <v>60.87929542713567</v>
       </c>
       <c r="L44" t="n">
-        <v>680.74</v>
+        <v>102.9591807537688</v>
       </c>
       <c r="M44" t="n">
-        <v>680.74</v>
+        <v>347.11</v>
       </c>
       <c r="N44" t="n">
         <v>680.74</v>
@@ -7669,22 +7669,22 @@
         <v>1348</v>
       </c>
       <c r="T44" t="n">
-        <v>1316.360336978221</v>
+        <v>1348</v>
       </c>
       <c r="U44" t="n">
-        <v>975.9562965741809</v>
+        <v>1348</v>
       </c>
       <c r="V44" t="n">
-        <v>649.8441509511265</v>
+        <v>1137.375364464491</v>
       </c>
       <c r="W44" t="n">
-        <v>315.1234681420886</v>
+        <v>802.6546816554529</v>
       </c>
       <c r="X44" t="n">
-        <v>26.96</v>
+        <v>514.4912135133643</v>
       </c>
       <c r="Y44" t="n">
-        <v>26.96</v>
+        <v>308.1099683792165</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>242.0549871683612</v>
+        <v>234.7555743113469</v>
       </c>
       <c r="C45" t="n">
-        <v>187.4086109607659</v>
+        <v>180.1091981037517</v>
       </c>
       <c r="D45" t="n">
-        <v>146.0574120741976</v>
+        <v>138.7579992171834</v>
       </c>
       <c r="E45" t="n">
-        <v>110.0249906379223</v>
+        <v>102.725577780908</v>
       </c>
       <c r="F45" t="n">
-        <v>77.05908928653147</v>
+        <v>69.75967642951723</v>
       </c>
       <c r="G45" t="n">
-        <v>58.27583406685453</v>
+        <v>50.97642120984029</v>
       </c>
       <c r="H45" t="n">
-        <v>34.25941285701424</v>
+        <v>26.96</v>
       </c>
       <c r="I45" t="n">
         <v>26.96</v>
@@ -7724,7 +7724,7 @@
         <v>376.6271300432672</v>
       </c>
       <c r="L45" t="n">
-        <v>678.9555789026183</v>
+        <v>642.6214735340828</v>
       </c>
       <c r="M45" t="n">
         <v>764.851865276942</v>
@@ -7742,28 +7742,28 @@
         <v>1348</v>
       </c>
       <c r="R45" t="n">
-        <v>1114.337235439373</v>
+        <v>1107.037822582359</v>
       </c>
       <c r="S45" t="n">
-        <v>955.8653563060701</v>
+        <v>948.5659434490558</v>
       </c>
       <c r="T45" t="n">
-        <v>857.1008231151375</v>
+        <v>849.8014102581233</v>
       </c>
       <c r="U45" t="n">
-        <v>762.9585214705806</v>
+        <v>755.6591086135664</v>
       </c>
       <c r="V45" t="n">
-        <v>654.3618879437926</v>
+        <v>647.0624750867784</v>
       </c>
       <c r="W45" t="n">
-        <v>527.7223496510364</v>
+        <v>520.4229367940222</v>
       </c>
       <c r="X45" t="n">
-        <v>413.7195825344834</v>
+        <v>406.4201696774692</v>
       </c>
       <c r="Y45" t="n">
-        <v>320.3949433767719</v>
+        <v>313.0955305197577</v>
       </c>
     </row>
     <row r="46">
@@ -7803,22 +7803,22 @@
         <v>1258.042754614309</v>
       </c>
       <c r="L46" t="n">
-        <v>1258.042754614309</v>
+        <v>1158.46190815588</v>
       </c>
       <c r="M46" t="n">
-        <v>1258.042754614309</v>
+        <v>1158.46190815588</v>
       </c>
       <c r="N46" t="n">
-        <v>1009.864602741933</v>
+        <v>1158.46190815588</v>
       </c>
       <c r="O46" t="n">
-        <v>690.3007112231402</v>
+        <v>1048.172121212121</v>
       </c>
       <c r="P46" t="n">
+        <v>707.7680808080809</v>
+      </c>
+      <c r="Q46" t="n">
         <v>367.3640404040404</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>26.96</v>
       </c>
       <c r="R46" t="n">
         <v>26.96</v>
@@ -7976,10 +7976,10 @@
         <v>842.9671979940761</v>
       </c>
       <c r="N2" t="n">
-        <v>645.9967628442865</v>
+        <v>775.1887470145589</v>
       </c>
       <c r="O2" t="n">
-        <v>370.8659751017306</v>
+        <v>241.6739909314582</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -8049,7 +8049,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L3" t="n">
-        <v>387.0245835623098</v>
+        <v>387.0245835622875</v>
       </c>
       <c r="M3" t="n">
         <v>471.6948204301074</v>
@@ -8201,7 +8201,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>358.1825389084069</v>
+        <v>12.18253890840691</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -8210,19 +8210,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>713.7752138238038</v>
+        <v>842.9671979940761</v>
       </c>
       <c r="N5" t="n">
-        <v>775.1887470145589</v>
+        <v>429.1887470145588</v>
       </c>
       <c r="O5" t="n">
-        <v>24.86597510173064</v>
+        <v>370.8659751017306</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>307.5546630557568</v>
       </c>
       <c r="Q5" t="n">
-        <v>489.7362672420583</v>
+        <v>398.989620016029</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,16 +8441,16 @@
         <v>12.18253890840691</v>
       </c>
       <c r="K8" t="n">
-        <v>317.7380854271357</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>256.8275061601678</v>
+        <v>222.5655915872827</v>
       </c>
       <c r="M8" t="n">
-        <v>848.9671979940761</v>
+        <v>848.967197994083</v>
       </c>
       <c r="N8" t="n">
-        <v>781.1887470145589</v>
+        <v>781.1887470145658</v>
       </c>
       <c r="O8" t="n">
         <v>24.86597510173064</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>143.7362672420583</v>
+        <v>495.7362672420652</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>12.18253890840691</v>
+        <v>371.1825389084233</v>
       </c>
       <c r="K11" t="n">
-        <v>324.7380854271357</v>
+        <v>229.2827633044889</v>
       </c>
       <c r="L11" t="n">
-        <v>263.5446778773393</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>855.9671979940761</v>
+        <v>855.9671979940925</v>
       </c>
       <c r="N11" t="n">
-        <v>788.1887470145589</v>
+        <v>788.1887470145753</v>
       </c>
       <c r="O11" t="n">
         <v>24.86597510173064</v>
@@ -8915,16 +8915,16 @@
         <v>12.18253890840691</v>
       </c>
       <c r="K14" t="n">
-        <v>229.2827633044749</v>
+        <v>324.7380854271516</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>855.9671979940761</v>
+        <v>855.9671979940862</v>
       </c>
       <c r="N14" t="n">
-        <v>788.1887470145589</v>
+        <v>788.1887470145689</v>
       </c>
       <c r="O14" t="n">
         <v>24.86597510173064</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>502.7362672420583</v>
+        <v>407.2809451194233</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>371.1825389084069</v>
+        <v>371.182538908417</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>229.2827633045062</v>
       </c>
       <c r="M17" t="n">
-        <v>855.9671979940761</v>
+        <v>855.9671979940862</v>
       </c>
       <c r="N17" t="n">
-        <v>658.4715103190338</v>
+        <v>429.1887470145588</v>
       </c>
       <c r="O17" t="n">
         <v>24.86597510173064</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>502.7362672420583</v>
+        <v>502.7362672420684</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>371.1825389084069</v>
+        <v>371.182538908417</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>267.7281002487494</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>726.2499612985511</v>
+        <v>496.9671979940761</v>
       </c>
       <c r="N20" t="n">
-        <v>788.1887470145589</v>
+        <v>429.1887470145588</v>
       </c>
       <c r="O20" t="n">
         <v>24.86597510173064</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>320.5546630557669</v>
       </c>
       <c r="Q20" t="n">
-        <v>502.7362672420583</v>
+        <v>502.7362672420684</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,19 +9623,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>371.1825389084069</v>
+        <v>12.18253890840691</v>
       </c>
       <c r="K23" t="n">
-        <v>324.7380854271357</v>
+        <v>324.7380854271516</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>855.9671979940761</v>
+        <v>855.9671979940863</v>
       </c>
       <c r="N23" t="n">
-        <v>429.1887470145588</v>
+        <v>788.1887470145691</v>
       </c>
       <c r="O23" t="n">
         <v>24.86597510173064</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>407.2809451193978</v>
+        <v>407.2809451194244</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,16 +9860,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>12.18253890840691</v>
+        <v>362.1825389084239</v>
       </c>
       <c r="K26" t="n">
-        <v>315.7380854271357</v>
+        <v>259.0917366123668</v>
       </c>
       <c r="L26" t="n">
-        <v>293.3536511852191</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>496.9671979940761</v>
+        <v>846.967197994093</v>
       </c>
       <c r="N26" t="n">
         <v>429.1887470145588</v>
@@ -9878,10 +9878,10 @@
         <v>24.86597510173064</v>
       </c>
       <c r="P26" t="n">
-        <v>311.5546630557568</v>
+        <v>311.5546630557738</v>
       </c>
       <c r="Q26" t="n">
-        <v>493.7362672420583</v>
+        <v>143.7362672420583</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,25 +10100,25 @@
         <v>12.18253890840691</v>
       </c>
       <c r="K29" t="n">
-        <v>315.7380854271357</v>
+        <v>315.7380854271516</v>
       </c>
       <c r="L29" t="n">
-        <v>293.3536511852191</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>496.9671979940761</v>
+        <v>846.9671979940912</v>
       </c>
       <c r="N29" t="n">
-        <v>429.1887470145588</v>
+        <v>684.0970612555515</v>
       </c>
       <c r="O29" t="n">
         <v>24.86597510173064</v>
       </c>
       <c r="P29" t="n">
-        <v>311.5546630557568</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>493.7362672420583</v>
+        <v>493.7362672420735</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,25 +10337,25 @@
         <v>12.18253890840691</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>253.334160854835</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>840.9671979940761</v>
+        <v>840.9671979940889</v>
       </c>
       <c r="N32" t="n">
-        <v>773.1887470145589</v>
+        <v>429.1887470145588</v>
       </c>
       <c r="O32" t="n">
         <v>24.86597510173064</v>
       </c>
       <c r="P32" t="n">
-        <v>305.5546630557568</v>
+        <v>305.5546630557696</v>
       </c>
       <c r="Q32" t="n">
-        <v>397.0704280968372</v>
+        <v>487.7362672420711</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10428,7 +10428,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O33" t="n">
-        <v>373.6978539842012</v>
+        <v>373.6978539842956</v>
       </c>
       <c r="P33" t="n">
         <v>219.1507118405495</v>
@@ -10574,25 +10574,25 @@
         <v>349.1825389084069</v>
       </c>
       <c r="K35" t="n">
-        <v>302.7380854271357</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>242.4335667662284</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>833.9671979940761</v>
+        <v>496.9671979940761</v>
       </c>
       <c r="N35" t="n">
         <v>429.1887470145588</v>
       </c>
       <c r="O35" t="n">
-        <v>24.86597510173064</v>
+        <v>361.8659751017306</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>208.1716521933641</v>
       </c>
       <c r="Q35" t="n">
-        <v>143.7362672420583</v>
+        <v>480.7362672420583</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10662,10 +10662,10 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N36" t="n">
-        <v>485.4085271713503</v>
+        <v>448.7074106374761</v>
       </c>
       <c r="O36" t="n">
-        <v>345.9806822670295</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P36" t="n">
         <v>219.1507118405495</v>
@@ -10808,7 +10808,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>258.7995280460142</v>
+        <v>349.1825389084069</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -10817,16 +10817,16 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>496.9671979940761</v>
+        <v>833.9671979940761</v>
       </c>
       <c r="N38" t="n">
-        <v>429.1887470145588</v>
+        <v>637.3603992079229</v>
       </c>
       <c r="O38" t="n">
-        <v>361.8659751017306</v>
+        <v>24.86597510173064</v>
       </c>
       <c r="P38" t="n">
-        <v>298.5546630557568</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>480.7362672420583</v>
@@ -10887,7 +10887,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>227.4647419277884</v>
+        <v>190.7636253939142</v>
       </c>
       <c r="K39" t="n">
         <v>295.8802408630135</v>
@@ -10896,7 +10896,7 @@
         <v>388.0893364597981</v>
       </c>
       <c r="M39" t="n">
-        <v>434.9937038962332</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N39" t="n">
         <v>485.4085271713503</v>
@@ -11045,28 +11045,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>349.1825389084069</v>
+        <v>262.8591257751378</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>294.4950653266332</v>
       </c>
       <c r="M41" t="n">
-        <v>496.9671979940761</v>
+        <v>833.9671979940761</v>
       </c>
       <c r="N41" t="n">
-        <v>429.1887470145588</v>
+        <v>766.1887470145589</v>
       </c>
       <c r="O41" t="n">
-        <v>361.8659751017306</v>
+        <v>24.86597510173064</v>
       </c>
       <c r="P41" t="n">
-        <v>298.5546630557568</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>390.3532563796655</v>
+        <v>143.7362672420583</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11130,10 +11130,10 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L42" t="n">
-        <v>351.3882199259239</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M42" t="n">
-        <v>471.6948204301074</v>
+        <v>434.9937038962332</v>
       </c>
       <c r="N42" t="n">
         <v>485.4085271713503</v>
@@ -11285,16 +11285,16 @@
         <v>12.18253890840691</v>
       </c>
       <c r="K44" t="n">
-        <v>302.7380854271357</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>280.8789037104716</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>496.9671979940761</v>
+        <v>743.5841871316834</v>
       </c>
       <c r="N44" t="n">
-        <v>429.1887470145588</v>
+        <v>766.1887470145589</v>
       </c>
       <c r="O44" t="n">
         <v>24.86597510173064</v>
@@ -11367,10 +11367,10 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>388.0893364597981</v>
+        <v>351.3882199259239</v>
       </c>
       <c r="M45" t="n">
-        <v>434.9937038962332</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N45" t="n">
         <v>485.4085271713503</v>
@@ -22518,7 +22518,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3.339155739849787</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -22566,7 +22566,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>24.28670755036723</v>
+        <v>20.94755181051733</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -22803,7 +22803,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>24.28670755036717</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -22812,7 +22812,7 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>24.28670755036725</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -22946,13 +22946,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.727611340735251</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.727611340735223</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -22992,7 +22992,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1.00190755036732</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -23049,7 +23049,7 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.001907550367264</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -23223,7 +23223,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>61.82846288588053</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -23241,7 +23241,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5.251211467346504</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23277,7 +23277,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>56.57725141859578</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -23460,10 +23460,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52.5755445710616</v>
+        <v>7.990595036019343</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -23472,7 +23472,7 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F14" t="n">
-        <v>4.889628708011855</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>5.838651177420502</v>
+        <v>5.838651177365591</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -23940,7 +23940,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>5.838651177365811</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>5.838651177422321</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24180,7 +24180,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3632896068686478</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -24189,7 +24189,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7494253122628576</v>
+        <v>0.7494253121827501</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24228,7 +24228,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4.725936258299129</v>
+        <v>5.089225865186137</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>93.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>54.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>48.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>48.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>47.48802555334788</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>49.25121146734648</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24459,19 +24459,19 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>132.7104291088556</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>229.4965164019308</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>293.1997488099172</v>
       </c>
       <c r="V26" t="n">
-        <v>8.742828056737494</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>190.0593976740326</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -24602,7 +24602,7 @@
         <v>145.6925786156646</v>
       </c>
       <c r="N28" t="n">
-        <v>126.8878524474065</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -24611,13 +24611,13 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>9.722266425597979</v>
+        <v>132.3421965471536</v>
       </c>
       <c r="R28" t="n">
-        <v>15.16963617787235</v>
+        <v>15.1696361778553</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>4.267922325806239</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24654,10 +24654,10 @@
         <v>48.33915573984979</v>
       </c>
       <c r="E29" t="n">
-        <v>42.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>42.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>41.48802555334787</v>
@@ -24696,13 +24696,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>126.7104291088556</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>119.4912429704401</v>
+        <v>44.25484158419704</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>287.1997488099172</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>43.58503799384475</v>
       </c>
       <c r="M31" t="n">
         <v>139.6925786156646</v>
@@ -24848,10 +24848,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>151.9272345410431</v>
+        <v>108.3421965471518</v>
       </c>
       <c r="R31" t="n">
-        <v>9.16963617787237</v>
+        <v>9.169636177857136</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -24888,7 +24888,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3391557398497866</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -24945,13 +24945,13 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.048307550305566</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.70915181051754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -25310,7 +25310,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.654811340735286</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -25319,7 +25319,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.654811340735364</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -25407,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.874751810495582</v>
+        <v>1.874751810517384</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -25547,7 +25547,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.65481134073525</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -25562,7 +25562,7 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.654811340735421</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -25596,22 +25596,22 @@
         <v>168.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>136.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>97.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>91.36328960686865</v>
+        <v>61.37892123874204</v>
       </c>
       <c r="F41" t="n">
-        <v>91.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>90.48802555334787</v>
       </c>
       <c r="H41" t="n">
-        <v>92.25121146734651</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,25 +25644,25 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>175.7104291088556</v>
       </c>
       <c r="T41" t="n">
-        <v>72.70995194819531</v>
+        <v>272.4965164019307</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>316.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>325.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>279.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>198.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -25790,19 +25790,19 @@
         <v>239.6963703536521</v>
       </c>
       <c r="O43" t="n">
-        <v>60.80657492941133</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>22.83530716434304</v>
       </c>
       <c r="Q43" t="n">
-        <v>65.72226642559799</v>
+        <v>79.26091902920319</v>
       </c>
       <c r="R43" t="n">
         <v>71.16963617787238</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>47.26792232580625</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25830,13 +25830,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>174.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>142.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>103.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>97.36328960686865</v>
@@ -25884,13 +25884,13 @@
         <v>181.7104291088556</v>
       </c>
       <c r="T44" t="n">
-        <v>247.1732500103698</v>
+        <v>278.4965164019307</v>
       </c>
       <c r="U44" t="n">
-        <v>5.1997488099172</v>
+        <v>342.1997488099172</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>114.3326349866697</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -25899,7 +25899,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>204.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -26018,25 +26018,25 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>98.58503799384475</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>194.6925786156646</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>245.6963703536521</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>207.1813635292839</v>
       </c>
       <c r="P46" t="n">
-        <v>46.12800305343421</v>
+        <v>28.83530716434304</v>
       </c>
       <c r="Q46" t="n">
         <v>71.72226642559799</v>
       </c>
       <c r="R46" t="n">
-        <v>414.1696361778723</v>
+        <v>77.16963617787238</v>
       </c>
       <c r="S46" t="n">
         <v>53.26792232580625</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>871935.3373781984</v>
+        <v>871935.3373781979</v>
       </c>
     </row>
     <row r="3">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3042199.883195803</v>
+        <v>3042199.883195808</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3763511.792640755</v>
+        <v>3763511.792640763</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4487386.355767607</v>
+        <v>4487386.355767617</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5211260.918894455</v>
+        <v>5211260.918894468</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5935135.482021303</v>
+        <v>5935135.482021319</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6620588.567247883</v>
+        <v>6620588.567247906</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7311801.324348015</v>
+        <v>7311801.324348042</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8034826.961471939</v>
+        <v>8034826.961471972</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8757338.443149045</v>
+        <v>8757338.443149073</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9481371.597553425</v>
+        <v>9481371.597553451</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10132795.10699747</v>
+        <v>10132795.1069975</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10778482.54055506</v>
+        <v>10778482.54055508</v>
       </c>
     </row>
   </sheetData>
@@ -26278,34 +26278,34 @@
         <v>1479674.313977614</v>
       </c>
       <c r="E2" t="n">
-        <v>1473985.206257078</v>
+        <v>1473985.206257083</v>
       </c>
       <c r="F2" t="n">
-        <v>1473985.206257078</v>
+        <v>1473985.206257083</v>
       </c>
       <c r="G2" t="n">
-        <v>1479221.933346176</v>
+        <v>1479221.933346181</v>
       </c>
       <c r="H2" t="n">
-        <v>1479221.933346176</v>
+        <v>1479221.933346181</v>
       </c>
       <c r="I2" t="n">
-        <v>1479221.933346175</v>
+        <v>1479221.93334618</v>
       </c>
       <c r="J2" t="n">
-        <v>1403316.967360254</v>
+        <v>1403316.967360261</v>
       </c>
       <c r="K2" t="n">
-        <v>1412478.242769843</v>
+        <v>1412478.242769849</v>
       </c>
       <c r="L2" t="n">
-        <v>1479576.444185614</v>
+        <v>1479576.44418562</v>
       </c>
       <c r="M2" t="n">
         <v>1479546.011174153</v>
       </c>
       <c r="N2" t="n">
-        <v>1479546.011174154</v>
+        <v>1479546.011174153</v>
       </c>
       <c r="O2" t="n">
         <v>1331169.780168255</v>
@@ -26330,7 +26330,7 @@
         <v>2112</v>
       </c>
       <c r="E3" t="n">
-        <v>316864</v>
+        <v>316864.0000000056</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>662429.5962486186</v>
+        <v>662414.3467159418</v>
       </c>
       <c r="C4" t="n">
-        <v>660385.8053318618</v>
+        <v>660370.5557991849</v>
       </c>
       <c r="D4" t="n">
-        <v>659247.423067487</v>
+        <v>659232.0843253953</v>
       </c>
       <c r="E4" t="n">
-        <v>654268.4461200004</v>
+        <v>654253.0057269323</v>
       </c>
       <c r="F4" t="n">
-        <v>652232.3336778827</v>
+        <v>652216.8932848143</v>
       </c>
       <c r="G4" t="n">
-        <v>652687.3325291143</v>
+        <v>652671.8921360457</v>
       </c>
       <c r="H4" t="n">
-        <v>650635.2986551895</v>
+        <v>650619.858262121</v>
       </c>
       <c r="I4" t="n">
-        <v>648580.4001086701</v>
+        <v>648564.9597156018</v>
       </c>
       <c r="J4" t="n">
-        <v>610931.7837333367</v>
+        <v>610916.4740343851</v>
       </c>
       <c r="K4" t="n">
-        <v>613319.6582398718</v>
+        <v>613304.3485409201</v>
       </c>
       <c r="L4" t="n">
-        <v>642943.0329629187</v>
+        <v>642927.827943594</v>
       </c>
       <c r="M4" t="n">
-        <v>641094.9469295284</v>
+        <v>641079.8977069284</v>
       </c>
       <c r="N4" t="n">
-        <v>639005.4144827758</v>
+        <v>638990.3652601747</v>
       </c>
       <c r="O4" t="n">
-        <v>568368.0107265246</v>
+        <v>568352.9615039246</v>
       </c>
       <c r="P4" t="n">
-        <v>561149.5779135365</v>
+        <v>561134.5286909363</v>
       </c>
     </row>
     <row r="5">
@@ -26434,28 +26434,28 @@
         <v>57078.283</v>
       </c>
       <c r="E5" t="n">
-        <v>56915.39999999999</v>
+        <v>56915.40000000097</v>
       </c>
       <c r="F5" t="n">
-        <v>56915.39999999999</v>
+        <v>56915.40000000097</v>
       </c>
       <c r="G5" t="n">
-        <v>57251.67600000001</v>
+        <v>57251.67600000097</v>
       </c>
       <c r="H5" t="n">
-        <v>57251.67600000001</v>
+        <v>57251.67600000097</v>
       </c>
       <c r="I5" t="n">
-        <v>57251.67600000001</v>
+        <v>57251.67600000097</v>
       </c>
       <c r="J5" t="n">
-        <v>52669.164</v>
+        <v>52669.16400000096</v>
       </c>
       <c r="K5" t="n">
-        <v>53173.57799999999</v>
+        <v>53173.57800000097</v>
       </c>
       <c r="L5" t="n">
-        <v>56844.09</v>
+        <v>56844.09000000097</v>
       </c>
       <c r="M5" t="n">
         <v>56670.697</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>565559.4887451865</v>
+        <v>565574.7382778635</v>
       </c>
       <c r="C6" t="n">
-        <v>760320.2796619439</v>
+        <v>760335.5291946206</v>
       </c>
       <c r="D6" t="n">
-        <v>761236.6079101269</v>
+        <v>761251.9466522189</v>
       </c>
       <c r="E6" t="n">
-        <v>445937.3601370774</v>
+        <v>445952.8005301444</v>
       </c>
       <c r="F6" t="n">
-        <v>764837.4725791949</v>
+        <v>764852.9129722682</v>
       </c>
       <c r="G6" t="n">
-        <v>760482.9248170615</v>
+        <v>760498.3652101348</v>
       </c>
       <c r="H6" t="n">
-        <v>771334.9586909866</v>
+        <v>771350.3990840593</v>
       </c>
       <c r="I6" t="n">
-        <v>773389.857237505</v>
+        <v>773405.2976305778</v>
       </c>
       <c r="J6" t="n">
-        <v>345092.019626917</v>
+        <v>345107.3293258751</v>
       </c>
       <c r="K6" t="n">
-        <v>741185.0065299707</v>
+        <v>741200.3162289285</v>
       </c>
       <c r="L6" t="n">
-        <v>732589.3212226956</v>
+        <v>732604.5262420252</v>
       </c>
       <c r="M6" t="n">
-        <v>779380.3672446246</v>
+        <v>779395.4164672241</v>
       </c>
       <c r="N6" t="n">
-        <v>783869.8996913786</v>
+        <v>783884.9489139778</v>
       </c>
       <c r="O6" t="n">
-        <v>518537.9724417302</v>
+        <v>518553.02166433</v>
       </c>
       <c r="P6" t="n">
-        <v>710539.2728780402</v>
+        <v>710554.3221006411</v>
       </c>
     </row>
   </sheetData>
@@ -26868,28 +26868,28 @@
         <v>352</v>
       </c>
       <c r="E4" t="n">
-        <v>359</v>
+        <v>359.0000000000159</v>
       </c>
       <c r="F4" t="n">
-        <v>359</v>
+        <v>359.0000000000159</v>
       </c>
       <c r="G4" t="n">
-        <v>359</v>
+        <v>359.0000000000159</v>
       </c>
       <c r="H4" t="n">
-        <v>359</v>
+        <v>359.0000000000159</v>
       </c>
       <c r="I4" t="n">
-        <v>359</v>
+        <v>359.0000000000159</v>
       </c>
       <c r="J4" t="n">
-        <v>350</v>
+        <v>350.0000000000159</v>
       </c>
       <c r="K4" t="n">
-        <v>350</v>
+        <v>350.0000000000159</v>
       </c>
       <c r="L4" t="n">
-        <v>344</v>
+        <v>344.0000000000159</v>
       </c>
       <c r="M4" t="n">
         <v>337</v>
@@ -26978,13 +26978,13 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>393</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
         <v>11</v>
@@ -26993,7 +26993,7 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>345</v>
@@ -27008,7 +27008,7 @@
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>245</v>
@@ -27085,7 +27085,7 @@
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>7.000000000008814</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -27326,7 +27326,7 @@
         <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>7.000000000015916</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27524,7 +27524,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>41.89430936900345</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -27533,7 +27533,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>212.1645934385184</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27578,7 +27578,7 @@
         <v>407</v>
       </c>
       <c r="X3" t="n">
-        <v>321.4226604696231</v>
+        <v>407</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27591,37 +27591,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>407</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>407</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>407</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>407</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>407</v>
       </c>
       <c r="G4" t="n">
-        <v>361.022358412268</v>
+        <v>407</v>
       </c>
       <c r="H4" t="n">
         <v>407</v>
       </c>
       <c r="I4" t="n">
-        <v>407</v>
+        <v>240.1412475854439</v>
       </c>
       <c r="J4" t="n">
         <v>26.72699801623563</v>
       </c>
       <c r="K4" t="n">
+        <v>274.4837246208152</v>
+      </c>
+      <c r="L4" t="n">
         <v>407</v>
-      </c>
-      <c r="L4" t="n">
-        <v>405.5850379938448</v>
       </c>
       <c r="M4" t="n">
         <v>407</v>
@@ -27645,22 +27645,22 @@
         <v>407</v>
       </c>
       <c r="T4" t="n">
-        <v>407</v>
+        <v>209.508336998061</v>
       </c>
       <c r="U4" t="n">
-        <v>407</v>
+        <v>150.9518011105235</v>
       </c>
       <c r="V4" t="n">
-        <v>407</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>407</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5">
@@ -27755,10 +27755,10 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>69.63343204011557</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27770,7 +27770,7 @@
         <v>330.7762569977419</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>212.1645934385184</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27797,10 +27797,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>192.3261369150208</v>
+        <v>407</v>
       </c>
       <c r="S6" t="n">
-        <v>117.8871603419698</v>
+        <v>407</v>
       </c>
       <c r="T6" t="n">
         <v>404.7768878590232</v>
@@ -27809,13 +27809,13 @@
         <v>400.2008786281113</v>
       </c>
       <c r="V6" t="n">
-        <v>168.8376835474157</v>
+        <v>407</v>
       </c>
       <c r="W6" t="n">
         <v>407</v>
       </c>
       <c r="X6" t="n">
-        <v>407</v>
+        <v>73.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27831,7 +27831,7 @@
         <v>407</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
         <v>407</v>
@@ -27843,22 +27843,22 @@
         <v>407</v>
       </c>
       <c r="G7" t="n">
-        <v>407</v>
+        <v>244.9230531693989</v>
       </c>
       <c r="H7" t="n">
         <v>407</v>
       </c>
       <c r="I7" t="n">
-        <v>288.2882872657933</v>
+        <v>407</v>
       </c>
       <c r="J7" t="n">
         <v>26.72699801623563</v>
       </c>
       <c r="K7" t="n">
-        <v>274.4837246208152</v>
+        <v>407</v>
       </c>
       <c r="L7" t="n">
-        <v>405.5850379938448</v>
+        <v>407</v>
       </c>
       <c r="M7" t="n">
         <v>407</v>
@@ -27879,25 +27879,25 @@
         <v>407</v>
       </c>
       <c r="S7" t="n">
-        <v>360.2679223258062</v>
+        <v>407</v>
       </c>
       <c r="T7" t="n">
         <v>209.508336998061</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9518011105235</v>
+        <v>407</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>219.1897854359856</v>
       </c>
       <c r="W7" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>407</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>407</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -28031,28 +28031,28 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>154.6833405621777</v>
       </c>
       <c r="R9" t="n">
-        <v>186.3261369150208</v>
+        <v>186.3261369150102</v>
       </c>
       <c r="S9" t="n">
-        <v>111.8871603419698</v>
+        <v>407</v>
       </c>
       <c r="T9" t="n">
-        <v>52.77688785902325</v>
+        <v>404.7768878590232</v>
       </c>
       <c r="U9" t="n">
-        <v>400.2008786281113</v>
+        <v>48.20087862810437</v>
       </c>
       <c r="V9" t="n">
         <v>407</v>
       </c>
       <c r="W9" t="n">
-        <v>407</v>
+        <v>80.37314290982161</v>
       </c>
       <c r="X9" t="n">
-        <v>319.6295257940639</v>
+        <v>196.4602026640519</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28077,10 +28077,10 @@
         <v>407</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>407</v>
       </c>
       <c r="G10" t="n">
-        <v>244.9230531693989</v>
+        <v>315.917392268908</v>
       </c>
       <c r="H10" t="n">
         <v>227.6969293803072</v>
@@ -28122,7 +28122,7 @@
         <v>209.508336998061</v>
       </c>
       <c r="U10" t="n">
-        <v>354.5632842422907</v>
+        <v>150.9518011105235</v>
       </c>
       <c r="V10" t="n">
         <v>407</v>
@@ -28226,7 +28226,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C12" t="n">
-        <v>361.0999124455193</v>
+        <v>2.099912445502881</v>
       </c>
       <c r="D12" t="n">
         <v>347.9376868977026</v>
@@ -28235,13 +28235,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>325.5954226674802</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>330.7762569977419</v>
       </c>
       <c r="I12" t="n">
         <v>212.1645934385184</v>
@@ -28268,13 +28268,13 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>154.6833405621777</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>400</v>
       </c>
       <c r="S12" t="n">
-        <v>326.1451709791103</v>
+        <v>182.9578500928344</v>
       </c>
       <c r="T12" t="n">
         <v>400</v>
@@ -28289,7 +28289,7 @@
         <v>400</v>
       </c>
       <c r="X12" t="n">
-        <v>400</v>
+        <v>60.86273944537115</v>
       </c>
       <c r="Y12" t="n">
         <v>399.3913927661343</v>
@@ -28302,28 +28302,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C13" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D13" t="n">
         <v>400</v>
       </c>
       <c r="E13" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F13" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G13" t="n">
         <v>400</v>
       </c>
       <c r="H13" t="n">
+        <v>227.6969293803072</v>
+      </c>
+      <c r="I13" t="n">
         <v>400</v>
-      </c>
-      <c r="I13" t="n">
-        <v>173.0000785709379</v>
       </c>
       <c r="J13" t="n">
         <v>26.72699801623563</v>
@@ -28356,22 +28356,22 @@
         <v>400</v>
       </c>
       <c r="T13" t="n">
+        <v>371.7418963129065</v>
+      </c>
+      <c r="U13" t="n">
+        <v>150.9518011105235</v>
+      </c>
+      <c r="V13" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W13" t="n">
+        <v>226.3728098387097</v>
+      </c>
+      <c r="X13" t="n">
+        <v>247.4436454301076</v>
+      </c>
+      <c r="Y13" t="n">
         <v>400</v>
-      </c>
-      <c r="U13" t="n">
-        <v>400</v>
-      </c>
-      <c r="V13" t="n">
-        <v>400</v>
-      </c>
-      <c r="W13" t="n">
-        <v>400</v>
-      </c>
-      <c r="X13" t="n">
-        <v>247.7091530785487</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="14">
@@ -28460,19 +28460,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>214.4323282964358</v>
+        <v>25.55655664631652</v>
       </c>
       <c r="C15" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
         <v>325.5954226674802</v>
@@ -28481,7 +28481,7 @@
         <v>330.7762569977419</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>202.9739396364624</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28529,7 +28529,7 @@
         <v>400</v>
       </c>
       <c r="Y15" t="n">
-        <v>399.3913927661343</v>
+        <v>40.39139276612431</v>
       </c>
     </row>
     <row r="16">
@@ -28545,13 +28545,13 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D16" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E16" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F16" t="n">
-        <v>274.3828559677419</v>
+        <v>384.012749506747</v>
       </c>
       <c r="G16" t="n">
         <v>400</v>
@@ -28563,10 +28563,10 @@
         <v>400</v>
       </c>
       <c r="J16" t="n">
-        <v>385.7269980162357</v>
+        <v>26.72699801623563</v>
       </c>
       <c r="K16" t="n">
-        <v>379.214129166392</v>
+        <v>400</v>
       </c>
       <c r="L16" t="n">
         <v>400</v>
@@ -28593,7 +28593,7 @@
         <v>400</v>
       </c>
       <c r="T16" t="n">
-        <v>209.508336998061</v>
+        <v>400</v>
       </c>
       <c r="U16" t="n">
         <v>400</v>
@@ -28605,7 +28605,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X16" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y16" t="n">
         <v>287.4653528494624</v>
@@ -28633,7 +28633,7 @@
         <v>404</v>
       </c>
       <c r="G17" t="n">
-        <v>404.0000000000105</v>
+        <v>404.000000000005</v>
       </c>
       <c r="H17" t="n">
         <v>404</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
         <v>361.0999124455193</v>
@@ -28742,7 +28742,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>154.6833405621777</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>404</v>
@@ -28754,19 +28754,19 @@
         <v>404</v>
       </c>
       <c r="U18" t="n">
-        <v>400.2008786281113</v>
+        <v>139.9367794368604</v>
       </c>
       <c r="V18" t="n">
+        <v>55.51066719151012</v>
+      </c>
+      <c r="W18" t="n">
+        <v>73.37314290981848</v>
+      </c>
+      <c r="X18" t="n">
         <v>404</v>
       </c>
-      <c r="W18" t="n">
-        <v>371.0736309025123</v>
-      </c>
-      <c r="X18" t="n">
-        <v>60.86273944538755</v>
-      </c>
       <c r="Y18" t="n">
-        <v>40.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -28776,7 +28776,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>404</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C19" t="n">
         <v>404</v>
@@ -28788,22 +28788,22 @@
         <v>404</v>
       </c>
       <c r="F19" t="n">
-        <v>274.3828559677419</v>
+        <v>404</v>
       </c>
       <c r="G19" t="n">
-        <v>404</v>
+        <v>244.9230531693989</v>
       </c>
       <c r="H19" t="n">
-        <v>227.6969293803072</v>
+        <v>326.0466100002124</v>
       </c>
       <c r="I19" t="n">
-        <v>404</v>
+        <v>173.0000785709379</v>
       </c>
       <c r="J19" t="n">
         <v>26.72699801623563</v>
       </c>
       <c r="K19" t="n">
-        <v>404</v>
+        <v>274.4837246208152</v>
       </c>
       <c r="L19" t="n">
         <v>404</v>
@@ -28827,22 +28827,22 @@
         <v>404</v>
       </c>
       <c r="S19" t="n">
-        <v>404</v>
+        <v>360.2679223258062</v>
       </c>
       <c r="T19" t="n">
         <v>209.508336998061</v>
       </c>
       <c r="U19" t="n">
-        <v>285.9389484073827</v>
+        <v>404</v>
       </c>
       <c r="V19" t="n">
         <v>404</v>
       </c>
       <c r="W19" t="n">
-        <v>226.3728098387097</v>
+        <v>404</v>
       </c>
       <c r="X19" t="n">
-        <v>247.4436454301076</v>
+        <v>404</v>
       </c>
       <c r="Y19" t="n">
         <v>287.4653528494624</v>
@@ -28870,7 +28870,7 @@
         <v>404</v>
       </c>
       <c r="G20" t="n">
-        <v>404.0000000000084</v>
+        <v>404.0000000000048</v>
       </c>
       <c r="H20" t="n">
         <v>404</v>
@@ -28934,10 +28934,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25.55655664632661</v>
+        <v>25.55655664631652</v>
       </c>
       <c r="C21" t="n">
-        <v>361.0999124455193</v>
+        <v>317.6628761565419</v>
       </c>
       <c r="D21" t="n">
         <v>347.9376868977026</v>
@@ -28982,7 +28982,7 @@
         <v>154.6833405621777</v>
       </c>
       <c r="R21" t="n">
-        <v>179.3261369150208</v>
+        <v>404</v>
       </c>
       <c r="S21" t="n">
         <v>404</v>
@@ -28994,16 +28994,16 @@
         <v>400.2008786281113</v>
       </c>
       <c r="V21" t="n">
-        <v>55.51066719152016</v>
+        <v>55.51066719151012</v>
       </c>
       <c r="W21" t="n">
         <v>404</v>
       </c>
       <c r="X21" t="n">
-        <v>404</v>
+        <v>60.86273944537751</v>
       </c>
       <c r="Y21" t="n">
-        <v>237.4909590074932</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="22">
@@ -29013,34 +29013,34 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>404</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C22" t="n">
         <v>404</v>
       </c>
       <c r="D22" t="n">
-        <v>404</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E22" t="n">
         <v>404</v>
       </c>
       <c r="F22" t="n">
-        <v>274.3828559677419</v>
+        <v>404</v>
       </c>
       <c r="G22" t="n">
-        <v>244.9230531693989</v>
+        <v>404</v>
       </c>
       <c r="H22" t="n">
         <v>404</v>
       </c>
       <c r="I22" t="n">
-        <v>244.291184679426</v>
+        <v>173.0000785709379</v>
       </c>
       <c r="J22" t="n">
         <v>26.72699801623563</v>
       </c>
       <c r="K22" t="n">
-        <v>274.4837246208152</v>
+        <v>404</v>
       </c>
       <c r="L22" t="n">
         <v>404</v>
@@ -29073,7 +29073,7 @@
         <v>150.9518011105235</v>
       </c>
       <c r="V22" t="n">
-        <v>404</v>
+        <v>404.0000000000045</v>
       </c>
       <c r="W22" t="n">
         <v>404</v>
@@ -29082,7 +29082,7 @@
         <v>404</v>
       </c>
       <c r="Y22" t="n">
-        <v>404</v>
+        <v>292.4307214738047</v>
       </c>
     </row>
     <row r="23">
@@ -29180,10 +29180,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>325.5954226674802</v>
@@ -29219,22 +29219,22 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>179.3261369150208</v>
+        <v>404</v>
       </c>
       <c r="S24" t="n">
-        <v>371.6019135548462</v>
+        <v>404</v>
       </c>
       <c r="T24" t="n">
         <v>404</v>
       </c>
       <c r="U24" t="n">
-        <v>400.2008786281113</v>
+        <v>41.20087862810107</v>
       </c>
       <c r="V24" t="n">
-        <v>404</v>
+        <v>55.51066719150995</v>
       </c>
       <c r="W24" t="n">
-        <v>404</v>
+        <v>172.1090437185781</v>
       </c>
       <c r="X24" t="n">
         <v>404</v>
@@ -29250,25 +29250,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>404</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C25" t="n">
         <v>404</v>
       </c>
       <c r="D25" t="n">
-        <v>404</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E25" t="n">
         <v>404</v>
       </c>
       <c r="F25" t="n">
-        <v>274.3828559677419</v>
+        <v>404</v>
       </c>
       <c r="G25" t="n">
         <v>404</v>
       </c>
       <c r="H25" t="n">
-        <v>404</v>
+        <v>325.4551525334105</v>
       </c>
       <c r="I25" t="n">
         <v>173.0000785709379</v>
@@ -29307,16 +29307,16 @@
         <v>209.508336998061</v>
       </c>
       <c r="U25" t="n">
-        <v>240.7931505497004</v>
+        <v>404</v>
       </c>
       <c r="V25" t="n">
         <v>404</v>
       </c>
       <c r="W25" t="n">
-        <v>226.3728098387097</v>
+        <v>404</v>
       </c>
       <c r="X25" t="n">
-        <v>404</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y25" t="n">
         <v>404</v>
@@ -29408,7 +29408,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>356</v>
+        <v>299.3414358530775</v>
       </c>
       <c r="C27" t="n">
         <v>356</v>
@@ -29453,19 +29453,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>154.6833405621777</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>188.3261369150208</v>
+        <v>188.3261369149973</v>
       </c>
       <c r="S27" t="n">
         <v>356</v>
       </c>
       <c r="T27" t="n">
-        <v>144.6580952908595</v>
+        <v>356</v>
       </c>
       <c r="U27" t="n">
-        <v>50.20087862811128</v>
+        <v>50.20087862809431</v>
       </c>
       <c r="V27" t="n">
         <v>356</v>
@@ -29493,28 +29493,28 @@
         <v>356</v>
       </c>
       <c r="D28" t="n">
-        <v>356</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E28" t="n">
-        <v>356</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F28" t="n">
-        <v>274.3828559677419</v>
+        <v>297.6528855659459</v>
       </c>
       <c r="G28" t="n">
         <v>356</v>
       </c>
       <c r="H28" t="n">
-        <v>227.6969293803072</v>
+        <v>356</v>
       </c>
       <c r="I28" t="n">
         <v>356</v>
       </c>
       <c r="J28" t="n">
+        <v>26.72699801623563</v>
+      </c>
+      <c r="K28" t="n">
         <v>356</v>
-      </c>
-      <c r="K28" t="n">
-        <v>274.4837246208152</v>
       </c>
       <c r="L28" t="n">
         <v>356</v>
@@ -29541,10 +29541,10 @@
         <v>356</v>
       </c>
       <c r="T28" t="n">
-        <v>209.508336998061</v>
+        <v>356</v>
       </c>
       <c r="U28" t="n">
-        <v>260.8251595077056</v>
+        <v>356</v>
       </c>
       <c r="V28" t="n">
         <v>356</v>
@@ -29645,13 +29645,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>362</v>
+        <v>332.8708192868706</v>
       </c>
       <c r="C30" t="n">
-        <v>346.1949257179777</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>342.6720972219126</v>
@@ -29666,7 +29666,7 @@
         <v>330.7762569977419</v>
       </c>
       <c r="I30" t="n">
-        <v>212.1645934385184</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29690,16 +29690,16 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>154.6833405621777</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>188.3261369150208</v>
+        <v>362</v>
       </c>
       <c r="S30" t="n">
-        <v>113.8871603419698</v>
+        <v>362</v>
       </c>
       <c r="T30" t="n">
-        <v>54.77688785902325</v>
+        <v>362</v>
       </c>
       <c r="U30" t="n">
         <v>362</v>
@@ -29724,10 +29724,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>362</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C31" t="n">
-        <v>362</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D31" t="n">
         <v>362</v>
@@ -29736,7 +29736,7 @@
         <v>362</v>
       </c>
       <c r="F31" t="n">
-        <v>362</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G31" t="n">
         <v>362</v>
@@ -29745,13 +29745,13 @@
         <v>362</v>
       </c>
       <c r="I31" t="n">
-        <v>182.7571194289779</v>
+        <v>362</v>
       </c>
       <c r="J31" t="n">
-        <v>26.72699801623563</v>
+        <v>362</v>
       </c>
       <c r="K31" t="n">
-        <v>274.4837246208152</v>
+        <v>362</v>
       </c>
       <c r="L31" t="n">
         <v>362</v>
@@ -29775,25 +29775,25 @@
         <v>362</v>
       </c>
       <c r="S31" t="n">
-        <v>360.2679223258062</v>
+        <v>362</v>
       </c>
       <c r="T31" t="n">
         <v>362</v>
       </c>
       <c r="U31" t="n">
-        <v>362</v>
+        <v>150.9518011105235</v>
       </c>
       <c r="V31" t="n">
-        <v>362</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W31" t="n">
-        <v>226.3728098387097</v>
+        <v>322.7992071015401</v>
       </c>
       <c r="X31" t="n">
         <v>362</v>
       </c>
       <c r="Y31" t="n">
-        <v>362</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="32">
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>233.9592470695005</v>
+        <v>233.959247069469</v>
       </c>
       <c r="S32" t="n">
         <v>410</v>
@@ -29882,16 +29882,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>40.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>86.41999703325672</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>3.937686897689858</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>339.6362423378769</v>
@@ -29927,16 +29927,16 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>154.6833405621777</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>303.5915038938984</v>
+        <v>410</v>
       </c>
       <c r="S33" t="n">
         <v>410</v>
       </c>
       <c r="T33" t="n">
-        <v>60.77688785902325</v>
+        <v>404.7768878590232</v>
       </c>
       <c r="U33" t="n">
         <v>400.2008786281113</v>
@@ -29945,7 +29945,7 @@
         <v>410</v>
       </c>
       <c r="W33" t="n">
-        <v>88.37314290982852</v>
+        <v>410</v>
       </c>
       <c r="X33" t="n">
         <v>410</v>
@@ -29961,25 +29961,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>287.1138003370787</v>
+        <v>410</v>
       </c>
       <c r="C34" t="n">
-        <v>272.7252466480447</v>
+        <v>410</v>
       </c>
       <c r="D34" t="n">
-        <v>285.5362180555555</v>
+        <v>410</v>
       </c>
       <c r="E34" t="n">
-        <v>280.9809048369565</v>
+        <v>410</v>
       </c>
       <c r="F34" t="n">
-        <v>274.3828559677419</v>
+        <v>410</v>
       </c>
       <c r="G34" t="n">
-        <v>283.8335358087248</v>
+        <v>410</v>
       </c>
       <c r="H34" t="n">
-        <v>227.6969293803072</v>
+        <v>410</v>
       </c>
       <c r="I34" t="n">
         <v>410</v>
@@ -29988,10 +29988,10 @@
         <v>26.72699801623563</v>
       </c>
       <c r="K34" t="n">
-        <v>410</v>
+        <v>274.4837246208152</v>
       </c>
       <c r="L34" t="n">
-        <v>410</v>
+        <v>405.5850379938448</v>
       </c>
       <c r="M34" t="n">
         <v>410</v>
@@ -30018,19 +30018,19 @@
         <v>209.508336998061</v>
       </c>
       <c r="U34" t="n">
-        <v>410</v>
+        <v>150.9518011105235</v>
       </c>
       <c r="V34" t="n">
-        <v>410</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W34" t="n">
-        <v>410</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X34" t="n">
-        <v>410</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y34" t="n">
-        <v>410</v>
+        <v>408.2621618241925</v>
       </c>
     </row>
     <row r="35">
@@ -30131,16 +30131,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>2.636242337876865</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>325.5954226674802</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>330.7762569977419</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>212.1645934385184</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30164,10 +30164,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>154.6833405621777</v>
+        <v>35.57770501068864</v>
       </c>
       <c r="R36" t="n">
-        <v>201.3261369150208</v>
+        <v>413</v>
       </c>
       <c r="S36" t="n">
         <v>413</v>
@@ -30176,19 +30176,19 @@
         <v>404.7768878590232</v>
       </c>
       <c r="U36" t="n">
-        <v>387.9458389530775</v>
+        <v>400.2008786281113</v>
       </c>
       <c r="V36" t="n">
         <v>413</v>
       </c>
       <c r="W36" t="n">
-        <v>413</v>
+        <v>95.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>413</v>
+        <v>82.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>399.3913927661343</v>
+        <v>62.39139276613435</v>
       </c>
     </row>
     <row r="37">
@@ -30210,7 +30210,7 @@
         <v>413</v>
       </c>
       <c r="F37" t="n">
-        <v>274.3828559677419</v>
+        <v>413</v>
       </c>
       <c r="G37" t="n">
         <v>244.9230531693989</v>
@@ -30225,10 +30225,10 @@
         <v>26.72699801623563</v>
       </c>
       <c r="K37" t="n">
-        <v>367.396416369981</v>
+        <v>274.4837246208152</v>
       </c>
       <c r="L37" t="n">
-        <v>413</v>
+        <v>405.5850379938448</v>
       </c>
       <c r="M37" t="n">
         <v>413</v>
@@ -30258,10 +30258,10 @@
         <v>150.9518011105235</v>
       </c>
       <c r="V37" t="n">
-        <v>413</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>226.3728098387097</v>
+        <v>401.9130093455564</v>
       </c>
       <c r="X37" t="n">
         <v>413</v>
@@ -30328,7 +30328,7 @@
         <v>233.9592470695005</v>
       </c>
       <c r="S38" t="n">
-        <v>413.0000000000221</v>
+        <v>413</v>
       </c>
       <c r="T38" t="n">
         <v>413</v>
@@ -30365,7 +30365,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>5.672097221912622</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
@@ -30377,7 +30377,7 @@
         <v>330.7762569977419</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>212.1645934385184</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30401,28 +30401,28 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>154.6833405621777</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>413</v>
       </c>
       <c r="S39" t="n">
-        <v>195.2948402422452</v>
+        <v>413</v>
       </c>
       <c r="T39" t="n">
-        <v>67.77688785902325</v>
+        <v>404.7768878590232</v>
       </c>
       <c r="U39" t="n">
         <v>400.2008786281113</v>
       </c>
       <c r="V39" t="n">
-        <v>413</v>
+        <v>77.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>413</v>
+        <v>95.37314290982852</v>
       </c>
       <c r="X39" t="n">
-        <v>413</v>
+        <v>116.9297772645559</v>
       </c>
       <c r="Y39" t="n">
         <v>399.3913927661343</v>
@@ -30435,10 +30435,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>287.1138003370787</v>
+        <v>413</v>
       </c>
       <c r="C40" t="n">
-        <v>272.7252466480447</v>
+        <v>304.0612385189732</v>
       </c>
       <c r="D40" t="n">
         <v>413</v>
@@ -30447,16 +30447,16 @@
         <v>413</v>
       </c>
       <c r="F40" t="n">
-        <v>297.6053885767164</v>
+        <v>413</v>
       </c>
       <c r="G40" t="n">
-        <v>244.9230531693989</v>
+        <v>413</v>
       </c>
       <c r="H40" t="n">
-        <v>227.6969293803072</v>
+        <v>413</v>
       </c>
       <c r="I40" t="n">
-        <v>173.0000785709379</v>
+        <v>413</v>
       </c>
       <c r="J40" t="n">
         <v>26.72699801623563</v>
@@ -30489,16 +30489,16 @@
         <v>413</v>
       </c>
       <c r="T40" t="n">
-        <v>413</v>
+        <v>209.508336998061</v>
       </c>
       <c r="U40" t="n">
-        <v>413</v>
+        <v>150.9518011105235</v>
       </c>
       <c r="V40" t="n">
-        <v>413</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W40" t="n">
-        <v>413</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X40" t="n">
         <v>247.4436454301076</v>
@@ -30614,7 +30614,7 @@
         <v>313</v>
       </c>
       <c r="I42" t="n">
-        <v>212.1645934385184</v>
+        <v>114.9381747100742</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30641,7 +30641,7 @@
         <v>154.6833405621777</v>
       </c>
       <c r="R42" t="n">
-        <v>215.7735812715559</v>
+        <v>313</v>
       </c>
       <c r="S42" t="n">
         <v>313</v>
@@ -30690,13 +30690,13 @@
         <v>313</v>
       </c>
       <c r="H43" t="n">
-        <v>307.8659044299907</v>
+        <v>313</v>
       </c>
       <c r="I43" t="n">
         <v>313</v>
       </c>
       <c r="J43" t="n">
-        <v>313</v>
+        <v>307.8659044299907</v>
       </c>
       <c r="K43" t="n">
         <v>313</v>
@@ -30851,7 +30851,7 @@
         <v>307</v>
       </c>
       <c r="I45" t="n">
-        <v>204.9381747100742</v>
+        <v>212.1645934385184</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30878,7 +30878,7 @@
         <v>154.6833405621777</v>
       </c>
       <c r="R45" t="n">
-        <v>307</v>
+        <v>299.7735812715558</v>
       </c>
       <c r="S45" t="n">
         <v>307</v>
@@ -34755,10 +34755,10 @@
         <v>346</v>
       </c>
       <c r="N2" t="n">
-        <v>216.8080158297277</v>
+        <v>346</v>
       </c>
       <c r="O2" t="n">
-        <v>346</v>
+        <v>216.8080158297276</v>
       </c>
       <c r="P2" t="n">
         <v>38.44533694424321</v>
@@ -34828,7 +34828,7 @@
         <v>214.3749772823007</v>
       </c>
       <c r="L3" t="n">
-        <v>304.3175186776137</v>
+        <v>304.3175186775915</v>
       </c>
       <c r="M3" t="n">
         <v>123.4650421645043</v>
@@ -34877,37 +34877,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>119.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>134.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>121.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>126.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>132.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>116.0993052428691</v>
+        <v>162.0769468306011</v>
       </c>
       <c r="H4" t="n">
         <v>179.3030706196928</v>
       </c>
       <c r="I4" t="n">
-        <v>233.9999214290621</v>
+        <v>67.14116901450596</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>132.5162753791848</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.414962006155235</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34931,22 +34931,22 @@
         <v>46.73207767419376</v>
       </c>
       <c r="T4" t="n">
-        <v>197.491663001939</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>256.0481988894765</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>207.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>159.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>119.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34980,7 +34980,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>34.26191457286433</v>
@@ -34989,19 +34989,19 @@
         <v>42.50493467336685</v>
       </c>
       <c r="M5" t="n">
-        <v>216.8080158297277</v>
+        <v>346</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>346</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
-        <v>38.44533694424321</v>
+        <v>346</v>
       </c>
       <c r="Q5" t="n">
-        <v>346</v>
+        <v>255.2533527739708</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35117,7 +35117,7 @@
         <v>119.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>134.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>121.4637819444445</v>
@@ -35129,22 +35129,22 @@
         <v>132.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>162.0769468306011</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>179.3030706196928</v>
       </c>
       <c r="I7" t="n">
-        <v>115.2882086948553</v>
+        <v>233.9999214290621</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>132.5162753791848</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.414962006155253</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>46.73207767419375</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>256.0481988894765</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>20.01947521976943</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>159.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>119.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35220,16 +35220,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>352</v>
+        <v>34.26191457286433</v>
       </c>
       <c r="L8" t="n">
-        <v>299.3324408335346</v>
+        <v>265.0705262606496</v>
       </c>
       <c r="M8" t="n">
-        <v>352</v>
+        <v>352.0000000000069</v>
       </c>
       <c r="N8" t="n">
-        <v>352</v>
+        <v>352.0000000000069</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>38.44533694424321</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>352.0000000000069</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35363,10 +35363,10 @@
         <v>126.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>132.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>70.99433909950911</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -35408,7 +35408,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>203.6114831317671</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>207.8296897837838</v>
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>359.0000000000164</v>
       </c>
       <c r="K11" t="n">
-        <v>359</v>
+        <v>263.5446778773533</v>
       </c>
       <c r="L11" t="n">
-        <v>306.0496125507061</v>
+        <v>42.50493467336685</v>
       </c>
       <c r="M11" t="n">
-        <v>359</v>
+        <v>359.0000000000164</v>
       </c>
       <c r="N11" t="n">
-        <v>359</v>
+        <v>359.0000000000164</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -35588,28 +35588,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D13" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G13" t="n">
         <v>155.0769468306011</v>
       </c>
       <c r="H13" t="n">
-        <v>172.3030706196928</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>226.9999214290621</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -35639,25 +35639,25 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>39.73207767419375</v>
+        <v>39.73207767419376</v>
       </c>
       <c r="T13" t="n">
-        <v>190.491663001939</v>
+        <v>162.2335593148455</v>
       </c>
       <c r="U13" t="n">
-        <v>249.0481988894765</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.2655076484411392</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="14">
@@ -35694,16 +35694,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>263.5446778773393</v>
+        <v>359.0000000000159</v>
       </c>
       <c r="L14" t="n">
         <v>42.50493467336685</v>
       </c>
       <c r="M14" t="n">
-        <v>359</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="N14" t="n">
-        <v>359</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -35712,7 +35712,7 @@
         <v>38.44533694424321</v>
       </c>
       <c r="Q14" t="n">
-        <v>359</v>
+        <v>263.544677877365</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35831,13 +35831,13 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>109.6298935390051</v>
       </c>
       <c r="G16" t="n">
         <v>155.0769468306011</v>
@@ -35849,10 +35849,10 @@
         <v>226.9999214290621</v>
       </c>
       <c r="J16" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>104.7304045455769</v>
+        <v>125.5162753791848</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35879,7 +35879,7 @@
         <v>39.73207767419375</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>190.491663001939</v>
       </c>
       <c r="U16" t="n">
         <v>249.0481988894765</v>
@@ -35891,7 +35891,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -35919,7 +35919,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5119744466625906</v>
+        <v>0.5119744466571337</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>359</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="K17" t="n">
         <v>34.26191457286433</v>
       </c>
       <c r="L17" t="n">
-        <v>42.50493467336685</v>
+        <v>271.7876979778731</v>
       </c>
       <c r="M17" t="n">
-        <v>359</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="N17" t="n">
-        <v>229.2827633044749</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -35949,7 +35949,7 @@
         <v>38.44533694424321</v>
       </c>
       <c r="Q17" t="n">
-        <v>359</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36062,7 +36062,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>116.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>131.2747533519553</v>
@@ -36074,22 +36074,22 @@
         <v>123.0190951630435</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>129.6171440322581</v>
       </c>
       <c r="G19" t="n">
-        <v>159.0769468306011</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>98.34968061990519</v>
       </c>
       <c r="I19" t="n">
-        <v>230.9999214290621</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>129.5162753791848</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -36113,22 +36113,22 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>43.73207767419375</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>134.9871472968591</v>
+        <v>253.0481988894765</v>
       </c>
       <c r="V19" t="n">
         <v>204.8296897837838</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>177.6271901612903</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>156.5563545698924</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -36156,7 +36156,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5119744466605443</v>
+        <v>0.5119744466569063</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>359</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="K20" t="n">
-        <v>34.26191457286433</v>
+        <v>301.9900148216137</v>
       </c>
       <c r="L20" t="n">
         <v>42.50493467336685</v>
       </c>
       <c r="M20" t="n">
-        <v>229.2827633044749</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>38.44533694424321</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="Q20" t="n">
-        <v>359</v>
+        <v>359.0000000000101</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36299,34 +36299,34 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>116.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>131.2747533519553</v>
       </c>
       <c r="D22" t="n">
-        <v>118.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>123.0190951630435</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>129.6171440322581</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>159.0769468306011</v>
       </c>
       <c r="H22" t="n">
         <v>176.3030706196928</v>
       </c>
       <c r="I22" t="n">
-        <v>71.29110610848802</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>129.5162753791848</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -36359,7 +36359,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>204.8296897837838</v>
+        <v>204.8296897837884</v>
       </c>
       <c r="W22" t="n">
         <v>177.6271901612903</v>
@@ -36368,7 +36368,7 @@
         <v>156.5563545698924</v>
       </c>
       <c r="Y22" t="n">
-        <v>116.5346471505376</v>
+        <v>4.965368624342396</v>
       </c>
     </row>
     <row r="23">
@@ -36402,19 +36402,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>359</v>
+        <v>359.0000000000159</v>
       </c>
       <c r="L23" t="n">
         <v>42.50493467336685</v>
       </c>
       <c r="M23" t="n">
-        <v>359</v>
+        <v>359.0000000000102</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>359.0000000000102</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -36423,7 +36423,7 @@
         <v>38.44533694424321</v>
       </c>
       <c r="Q23" t="n">
-        <v>263.5446778773395</v>
+        <v>263.5446778773662</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36536,25 +36536,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>116.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>131.2747533519553</v>
       </c>
       <c r="D25" t="n">
-        <v>118.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>123.0190951630435</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>129.6171440322581</v>
       </c>
       <c r="G25" t="n">
         <v>159.0769468306011</v>
       </c>
       <c r="H25" t="n">
-        <v>176.3030706196928</v>
+        <v>97.75822315310332</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -36593,16 +36593,16 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>89.84134943917689</v>
+        <v>253.0481988894765</v>
       </c>
       <c r="V25" t="n">
         <v>204.8296897837838</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>177.6271901612903</v>
       </c>
       <c r="X25" t="n">
-        <v>156.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>116.5346471505376</v>
@@ -36639,16 +36639,16 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>350.000000000017</v>
       </c>
       <c r="K26" t="n">
-        <v>350</v>
+        <v>293.3536511852312</v>
       </c>
       <c r="L26" t="n">
-        <v>335.8585858585859</v>
+        <v>42.50493467336685</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>350.000000000017</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -36657,10 +36657,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>350</v>
+        <v>350.000000000017</v>
       </c>
       <c r="Q26" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36779,28 +36779,28 @@
         <v>83.27475335195533</v>
       </c>
       <c r="D28" t="n">
-        <v>70.46378194444452</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>75.01909516304346</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>23.27002959820394</v>
       </c>
       <c r="G28" t="n">
         <v>111.0769468306011</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>128.3030706196928</v>
       </c>
       <c r="I28" t="n">
         <v>182.9999214290621</v>
       </c>
       <c r="J28" t="n">
-        <v>329.2730019837644</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>81.51627537918483</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -36827,10 +36827,10 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>146.491663001939</v>
       </c>
       <c r="U28" t="n">
-        <v>109.8733583971821</v>
+        <v>205.0481988894765</v>
       </c>
       <c r="V28" t="n">
         <v>156.8296897837838</v>
@@ -36879,25 +36879,25 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>350</v>
+        <v>350.0000000000159</v>
       </c>
       <c r="L29" t="n">
-        <v>335.8585858585859</v>
+        <v>42.50493467336685</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>350.0000000000152</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>254.9083142409926</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>350</v>
+        <v>38.44533694424321</v>
       </c>
       <c r="Q29" t="n">
-        <v>350</v>
+        <v>350.0000000000152</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37010,10 +37010,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>74.88619966292134</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>89.27475335195533</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>76.46378194444452</v>
@@ -37022,7 +37022,7 @@
         <v>81.01909516304346</v>
       </c>
       <c r="F31" t="n">
-        <v>87.61714403225807</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>117.0769468306011</v>
@@ -37031,13 +37031,13 @@
         <v>134.3030706196928</v>
       </c>
       <c r="I31" t="n">
-        <v>9.757040858040005</v>
+        <v>188.9999214290621</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>335.2730019837644</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>87.51627537918483</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37061,25 +37061,25 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.732077674193746</v>
       </c>
       <c r="T31" t="n">
         <v>152.491663001939</v>
       </c>
       <c r="U31" t="n">
-        <v>211.0481988894765</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>162.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>96.42639726283038</v>
       </c>
       <c r="X31" t="n">
         <v>114.5563545698924</v>
       </c>
       <c r="Y31" t="n">
-        <v>74.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -37116,28 +37116,28 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>34.26191457286432</v>
+        <v>287.5960754276993</v>
       </c>
       <c r="L32" t="n">
         <v>42.50493467336685</v>
       </c>
       <c r="M32" t="n">
-        <v>344</v>
+        <v>344.0000000000128</v>
       </c>
       <c r="N32" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>344</v>
+        <v>344.0000000000128</v>
       </c>
       <c r="Q32" t="n">
-        <v>253.334160854779</v>
+        <v>344.0000000000128</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>-3.146484195527555e-11</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -37207,7 +37207,7 @@
         <v>172.1079935048813</v>
       </c>
       <c r="O33" t="n">
-        <v>266.7612751992514</v>
+        <v>266.7612751993458</v>
       </c>
       <c r="P33" t="n">
         <v>141.1853064014457</v>
@@ -37247,25 +37247,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>122.8861996629213</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>137.2747533519553</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>124.4637819444445</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>129.0190951630435</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>135.6171440322581</v>
       </c>
       <c r="G34" t="n">
-        <v>38.91048263932591</v>
+        <v>165.0769468306011</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>182.3030706196928</v>
       </c>
       <c r="I34" t="n">
         <v>236.9999214290621</v>
@@ -37274,10 +37274,10 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>135.5162753791848</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>4.414962006155253</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -37304,19 +37304,19 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>259.0481988894765</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>210.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>183.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>162.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>122.5346471505376</v>
+        <v>120.7968089747301</v>
       </c>
     </row>
     <row r="35">
@@ -37353,25 +37353,25 @@
         <v>337</v>
       </c>
       <c r="K35" t="n">
+        <v>34.26191457286433</v>
+      </c>
+      <c r="L35" t="n">
+        <v>42.50493467336685</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>337</v>
       </c>
-      <c r="L35" t="n">
-        <v>284.9385014395953</v>
-      </c>
-      <c r="M35" t="n">
+      <c r="P35" t="n">
+        <v>246.6169891376073</v>
+      </c>
+      <c r="Q35" t="n">
         <v>337</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>38.44533694424321</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37441,10 +37441,10 @@
         <v>123.4650421645043</v>
       </c>
       <c r="N36" t="n">
-        <v>172.1079935048813</v>
+        <v>135.4068769710071</v>
       </c>
       <c r="O36" t="n">
-        <v>239.0441034820797</v>
+        <v>275.7452200159539</v>
       </c>
       <c r="P36" t="n">
         <v>141.1853064014457</v>
@@ -37496,7 +37496,7 @@
         <v>132.0190951630435</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>138.6171440322581</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>92.91269174916579</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>7.414962006155253</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37544,10 +37544,10 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>213.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>175.5401995068466</v>
       </c>
       <c r="X37" t="n">
         <v>165.5563545698924</v>
@@ -37587,7 +37587,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>246.6169891376072</v>
+        <v>337</v>
       </c>
       <c r="K38" t="n">
         <v>34.26191457286433</v>
@@ -37596,16 +37596,16 @@
         <v>42.50493467336685</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>208.1716521933641</v>
       </c>
       <c r="O38" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>337</v>
+        <v>38.44533694424321</v>
       </c>
       <c r="Q38" t="n">
         <v>337</v>
@@ -37666,7 +37666,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>138.8241439735248</v>
+        <v>102.1230274396506</v>
       </c>
       <c r="K39" t="n">
         <v>214.3749772823007</v>
@@ -37675,7 +37675,7 @@
         <v>305.3822715751021</v>
       </c>
       <c r="M39" t="n">
-        <v>86.76392563063003</v>
+        <v>123.4650421645043</v>
       </c>
       <c r="N39" t="n">
         <v>172.1079935048813</v>
@@ -37721,10 +37721,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>125.8861996629213</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>31.33599187092851</v>
       </c>
       <c r="D40" t="n">
         <v>127.4637819444445</v>
@@ -37733,16 +37733,16 @@
         <v>132.0190951630435</v>
       </c>
       <c r="F40" t="n">
-        <v>23.22253260897446</v>
+        <v>138.6171440322581</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>168.0769468306011</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>185.3030706196928</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>239.9999214290621</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -37751,7 +37751,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>7.414962006155235</v>
+        <v>7.414962006155253</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -37772,19 +37772,19 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>52.73207767419376</v>
+        <v>52.73207767419375</v>
       </c>
       <c r="T40" t="n">
-        <v>203.491663001939</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>262.0481988894765</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>213.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>186.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -37824,28 +37824,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>337</v>
+        <v>250.6765868667309</v>
       </c>
       <c r="K41" t="n">
         <v>34.26191457286433</v>
       </c>
       <c r="L41" t="n">
-        <v>42.50493467336685</v>
+        <v>337</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="O41" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>337</v>
+        <v>38.44533694424321</v>
       </c>
       <c r="Q41" t="n">
-        <v>246.6169891376072</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37909,10 +37909,10 @@
         <v>214.3749772823007</v>
       </c>
       <c r="L42" t="n">
-        <v>268.6811550412279</v>
+        <v>305.3822715751021</v>
       </c>
       <c r="M42" t="n">
-        <v>123.4650421645043</v>
+        <v>86.76392563063003</v>
       </c>
       <c r="N42" t="n">
         <v>172.1079935048813</v>
@@ -37976,13 +37976,13 @@
         <v>68.07694683060112</v>
       </c>
       <c r="H43" t="n">
-        <v>80.16897504968357</v>
+        <v>85.30307061969286</v>
       </c>
       <c r="I43" t="n">
         <v>139.9999214290621</v>
       </c>
       <c r="J43" t="n">
-        <v>286.2730019837644</v>
+        <v>281.138906413755</v>
       </c>
       <c r="K43" t="n">
         <v>38.51627537918483</v>
@@ -38064,16 +38064,16 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
+        <v>34.26191457286431</v>
+      </c>
+      <c r="L44" t="n">
+        <v>42.50493467336683</v>
+      </c>
+      <c r="M44" t="n">
+        <v>246.6169891376072</v>
+      </c>
+      <c r="N44" t="n">
         <v>337</v>
-      </c>
-      <c r="L44" t="n">
-        <v>323.3838383838385</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -38146,10 +38146,10 @@
         <v>214.3749772823007</v>
       </c>
       <c r="L45" t="n">
-        <v>305.3822715751021</v>
+        <v>268.6811550412279</v>
       </c>
       <c r="M45" t="n">
-        <v>86.76392563063003</v>
+        <v>123.4650421645043</v>
       </c>
       <c r="N45" t="n">
         <v>172.1079935048813</v>
